--- a/docs/CONNECTSPHERE BACKLOGS CAA 161026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 161026.xlsx
@@ -1728,8 +1728,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>As an Event Organiser, I want to fill in and correct the registration setup on my event request, and read the registration dates clearly, so that a request that left the registration setup blank can still be completed for approval.
-Fix story created by the Product Owner on 12 October 2026 (Jira SCRUM-176) for two gaps found in E03-S07, which stays Done (T-74): the Organiser's edit form had no registration setup field, and the registration date labels were laid out wrongly. Delivered in #247.</t>
+          <t>As an Event Organiser, I want to fill in and correct the registration setup on my event request, and read the registration dates clearly, so that a request that left the registration setup blank can still be completed for approval.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5419,8 +5418,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>As an Event Organiser, I want to fill in and correct the registration setup on my event request, and read the registration dates clearly, so that a request that left the registration setup blank can still be completed for approval.
-Fix story created by the Product Owner on 12 October 2026 (Jira SCRUM-176) for two gaps found in E03-S07, which stays Done (T-74): the Organiser's edit form had no registration setup field, and the registration date labels were laid out wrongly. Delivered in #247.</t>
+          <t>As an Event Organiser, I want to fill in and correct the registration setup on my event request, and read the registration dates clearly, so that a request that left the registration setup blank can still be completed for approval.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">

--- a/docs/CONNECTSPHERE BACKLOGS CAA 161026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 161026.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1706,28 +1706,83 @@
       <c r="I23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>E03-S12</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Show consistent Organiser save success status</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser, I want confirmation of a saved event edit to use the shared success Alert so that I can recognise the same clear save outcome used on the Coordinator's event page.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Shared success Alert after a saved edit
+Given I may edit an event When a changed field saves successfully Then the event detail shows the existing field-specific saved message through the shared Alert with tone="success", retaining role="status" rather than replacing it with an urgent alert or plain paragraph.
+Scenario 2 - Saved data and audit survive reload
+Given an allowed event edit succeeds When the record reloads and I reopen it Then the changed value is retained and its existing activity-log entry remains available, with no extra save or audit write caused by rendering the confirmation.
+Scenario 3 - Failure cannot report success
+Given a new edit is invalid or its save request fails When I attempt to save Then the existing validation or error feedback remains and no success Alert claims that attempt was saved; starting a new edit clears the previous save confirmation.
+Scenario 4 - Cancellation and permissions unchanged
+Given I cancel an edit or attempt a field I cannot edit under the current event status and access rules When the attempt ends Then cancellation produces no save confirmation or mutation, and existing restrictions and change-request routing remain in force.
+Checklist
+- Reuse frontend/src/shared/feedback.tsx Alert in frontend/src/features/organiser/ClientEvents.tsx; preserve field-specific text and polite status semantics
+- Cover successful save/reload/audit, invalid input, failed request after a prior success, cancellation and restricted fields with TC_E03S12_01 to _05
+- Leave the Coordinator save flow, all other Organiser workflows, permissions and notifications unchanged; no redesign or new notification
+- Obtain human review of code and test cases and future manual evidence before claiming delivery; this definition does not execute those cases</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>T-93</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Le Xin</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>E04-S02</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Create a multi-session event</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to define an event made up of one or more Sessions so that each Session's requirements can be planned separately.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Sessions hold their own requirements
 Given I am creating an event When I add one or more Sessions Then each Session stores its date, time, expected attendance, venue requirements, and equipment requirements beneath the Event
@@ -1747,43 +1802,43 @@
 - Delete a Session and release its confirmed booking with notification and history</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>C-19, C-62, C-107, T-48, T-79, T-85</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>E05-S01</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Maintain the venue catalogue</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to add and update venue records so that Event Coordinators search against accurate information.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue added and searchable
 Given I am adding a venue When I save it with location, capacity, facilities, accessibility features, supported layouts and operating hours Then it becomes searchable by Event Coordinators
@@ -1802,47 +1857,47 @@
 - Be blocked from retiring a venue with future bookings, with those bookings identified</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>T-13, T-18, B-05</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>E05-S02</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Match layout requirements to venue capacity</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the room layouts supported by a venue and the maximum capacity for each layout, so that Event Coordinators only consider arrangements the venue can accommodate.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Layout and capacity stored
 Given I am editing a venue When I add a supported layout with its maximum capacity Then it is stored against that venue
@@ -1858,47 +1913,47 @@
 - Be warned when adding a layout that already exists</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>T-45, B-07</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>E05-S03</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>View the venue availability calendar</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to view a venue's calendar so that I can see when the venue is free, pending, confirmed or blocked.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Four states distinguishable
 Given a venue has bookings and blocks in a period When I open its calendar for that period Then each entry is shown as Free, Tentative, Confirmed or Blocked, and the states are visually distinguishable
@@ -1915,43 +1970,43 @@
 - See periods I cannot view marked unavailable without any event detail</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>C-40, C-60, T-17, T-49</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>E05-S04</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Block a venue for maintenance</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to block a venue for maintenance, renovation or safety reasons so that it is not offered for events during that period.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Free period blocked
 Given a venue has no bookings in a period When I block that period and record a reason Then the venue no longer appears as available for those dates
@@ -1967,44 +2022,44 @@
 - Confirm affected Event Coordinators are notified when a block affects an upcoming event</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>E05-S05</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Apply setup and turnaround time</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the setup and turnaround time each venue requires so that every availability and conflict check accounts for the time needed to prepare the room before an event and reset it afterwards.
 Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03, and Scenario 7 here rather than in E06-S01, because both of those stories are Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Buffers recorded on the venue
 Given I am creating or editing a venue When I enter a setup time and a turnaround time in whole minutes, either of which may be 0, and save Then both values are stored against the venue and shown on its detail, and every venue that existed before this story has both values at 0
@@ -2028,44 +2083,44 @@
 - Never have a booking released automatically because a buffer changed</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>C-65, T-66, T-73, T-74, O-20, O-21, O-22 (supersedes C-18, C-38)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mark a venue temporarily unavailable over existing bookings</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to mark a venue temporarily unavailable for maintenance, equipment failure, renovation, a safety concern or another operational reason, even when events are already booked in it, so that affected bookings are identified and their Coordinators can arrange an alternative without the events themselves being cancelled.
 New story from the Week 7 Customer Changes (C-66). It supersedes E05-S04 Scenario 2, which refused a block over a confirmed booking; E05-S04 is in the Sprint 2 sprint backlog and is not edited (T-67, T-74). Estimate to be set by planning poker at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Unavailability recorded with a reason
 Given I am viewing a venue When I mark it unavailable for a period and choose a reason category from maintenance, equipment failure, renovation, safety concern or other, with a free-text note Then the unavailability is saved with the period, the category, the note and my identity, and the calendar shows the period as Blocked
@@ -2089,41 +2144,41 @@
 - Confirm E05-S04's existing block, shorten and remove behaviour still works for periods with no bookings</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>C-66, C-48, C-61, T-28, T-67, T-74, O-23, O-24, O-25, O-26</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -2142,43 +2197,43 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>B-08</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -2207,43 +2262,43 @@
 - Identify outside operating hours as an advisory failure in E06-S02, without adding that rule to E06-S01</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-48 (supersedes T-21), T-77, B-08</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -2304,43 +2359,43 @@
 - Complete TC_E06S03_09 to _13 under the current Sprint 3 plan; record anything unfinished honestly at sprint close (PO confirmation, 16 October; T-94)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, T-78, O-27, O-29, O-30, T-94, T-95, T-96</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -2364,48 +2419,48 @@
 - Verify all three booking-log outcomes under TC_E06S04_05, TC_E06S04_06 and TC_E06S04_07</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66, T-75, T-76</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
 The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
@@ -2438,43 +2493,43 @@
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, T-78, T-92, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
@@ -2495,43 +2550,43 @@
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -2548,43 +2603,43 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -2600,43 +2655,43 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -2652,43 +2707,43 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -2707,43 +2762,43 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -2756,43 +2811,43 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -2808,43 +2863,43 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -2863,39 +2918,39 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E07-S08</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Link equipment requests and reservations to Sessions</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want equipment requests and reservations to identify the Session they support so that availability and fulfilment use the correct Session period.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request linked to its Session
 Given an Event has multiple Sessions When an Event Coordinator records equipment needed for one Session Then the request is linked to that Session and remains part of the Event
@@ -2912,37 +2967,37 @@
 - Keep technical-support staff assignment event-level</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>C-107, T-74, T-79</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E07-S09</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Preserve reservation warnings when stock reductions overlap withdrawals</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want catalogue stock reductions to account for dated equipment withdrawals so that reservations which no longer fit are flagged and their Coordinators are notified.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reduced usable stock flags reservations
 Given an item has total stock 10, four units withdrawn and five units reserved for the same future period When I reduce total stock to 8 Then the save succeeds, the reservation remains reserved but is marked for review, and its assigned active Coordinator receives one notification and an outbox record
@@ -2958,42 +3013,42 @@
 - Roll back stock, flags and notification/outbox writes together on failure</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.
 Amended in place for the Week 7 Customer Changes (C-70, T-71; this story is To Do, T-74). Completing the arrangements no longer sets Confirmed directly: it lets the Coordinator submit the event for its Operational Safety Check, which moves it to the new Safety Review status, and the Safety Officer's approval (E08-S06) is what sets Confirmed. The readiness checks below are unchanged in substance; what they now gate is the submission. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event submitted for safety review
 Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, its full requested equipment is reserved and any requested technical support is assigned When I submit the event for its Operational Safety Check Then the status becomes Safety Review, the Safety Officer is notified, the Organiser is told the event is awaiting its safety check, and the event becomes Confirmed only when the Safety Officer approves it (E08-S06) (C-67, T-68, C-70, T-71; assumes O-28, O-39, O-40)
@@ -3019,43 +3074,43 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28, C-70, T-71, T-74, O-39, O-40</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a confirmed event to return to Planning when an arrangement requires it so that the system reflects the event's readiness and starts safety review at the right time.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Manual reversion records a reason
 Given an event is Confirmed When I deliberately revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -3076,43 +3131,43 @@
 - Retain earlier safety decisions in history without reusing them</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28, C-70, T-71, C-120, T-81, C-132, T-82</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -3130,44 +3185,44 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E08-S06</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Conduct the Operational Safety Check as the Safety Officer</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As a Safety Officer, I want to review the operational safety of each event whose venue and technical arrangements are confirmed, and approve it, reject its safety arrangement or request changes, so that no event proceeds to preparation until it is safe to run.
 New story from the Week 7 Customer Changes (C-70) and the seventh role (T-72). The Safety Review status it works on sits between Planning and Confirmed as an interim placement (T-71); O-39 asks the customer to confirm. The customer guarantees a response, so there is no timeout path. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events awaiting review listed with what the check needs
 Given events are in Safety Review When I open my queue Then each shows the event name, date and time, every confirmed venue with its capacity, layout and known restrictions, expected attendance, accessibility requirements, equipment and its placement, and the time it entered Safety Review, oldest first
@@ -3200,41 +3255,41 @@
 - Confirm every decision is in the activity log</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>C-70, T-71, T-72, T-73, T-74, O-39, O-40, O-41, O-42, O-43</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register once for a confirmed Event and select the Sessions I will attend so that my place is reserved across the Event I chose.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open Event
 Given an Event is Confirmed, registration is open, and selected Sessions have capacity When I submit the required registration information and select one or more Sessions Then one active Event-level registration records those Sessions and I receive a confirmation with the Event and selected Session details
@@ -3255,43 +3310,43 @@
 - See the primary Event venue and the venue for each selected Session</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-35, C-67, C-97, C-107, T-68, T-78, T-79, T-85</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want the system to enforce each selected Session's approved layout capacity and the combined Event capacity so that registrations do not exceed either limit.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Both capacity limits enforced
 Given a registration selects one or more Sessions When the request is within each selected Session's approved layout capacity and within the combined Event capacity Then it may be confirmed; if either limit would be exceeded it is not confirmed as an approved seat (C-78, T-85)
@@ -3317,43 +3372,43 @@
 - Allow manual VIP additions only within both limits and block them at either limit</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, C-78, C-98, T-30, T-31, T-50, T-85, B-11, O-50</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set one registration and withdrawal window for the Event so that attendees can select Sessions within a consistent Event-level period.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the Event-level registration opening date has not been reached When an Attendee views the Event Then registration is shown as not yet open and the opening date is stated
@@ -3372,43 +3427,43 @@
 - Warn when the closing date is after the Event has started</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42, T-79, T-85</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given the combined Event capacity is full and its Event-level waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released (Session-specific waiting-list behavior remains open under O-50)
@@ -3427,43 +3482,43 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10, O-50</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my Event registration so that my Event place and places in all selected Sessions are released together.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn from Event and Sessions
 Given I have an active Event registration selecting one or more Sessions and the withdrawal deadline has not passed When I withdraw Then the Event registration is cancelled and its approved places are released from every selected Session and from the combined Event capacity
@@ -3475,43 +3530,43 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10, T-79, T-85</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -3527,43 +3582,43 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -3581,43 +3636,43 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my Event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the Event
@@ -3639,43 +3694,43 @@
 - Confirm Pending requests become Obsolete with history when the Event becomes Completed or Cancelled</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, C-77, T-16, T-88</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to identify which Session arrangements a change affects so that I re-check the right bookings and reservations.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Session attendance beyond capacity flagged
 Given a Session has a confirmed venue booking When its expected attendance changes Then each booking whose own headcount is set uses that headcount, otherwise it uses the Session attendance; only a booking whose governing headcount exceeds capacity is flagged and Venue Staff are notified
@@ -3698,43 +3753,43 @@
 - Notify staff responsible for the affected arrangements</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27, C-107, T-79</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an Event and release its Session arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled and Session arrangements released
 Given an Event Organiser requests cancellation When I cancel the Event and record a reason Then its status becomes Cancelled, all Session venue bookings and equipment reservations are released, calendars/availability are updated, and affected staff are notified
@@ -3755,44 +3810,44 @@
 - Close Pending change requests as Obsolete with history</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, C-77, T-07, T-48, T-79, T-88</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>E10-S05</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Handle a venue lost from a confirmed event</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
 Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Lost venue flags the event
 Given my event has a Pending or Confirmed venue booking When Venue Staff mark that venue unavailable over the booking's period (E05-S06) Then I am notified, the booking shows as Conflicting on the event, and the event is flagged as needing alternative arrangements while its status and every other arrangement stay as they were (assumes O-24)
@@ -3810,43 +3865,43 @@
 - Confirm the Organiser and registered Attendees are told of the venue change only when it actually happens</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>C-66, C-61, T-28, T-67, T-73, T-74, O-24, O-25</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -3874,43 +3929,43 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70, C-70, T-71</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log; access-denial entries are not shown in that log
@@ -3932,15 +3987,73 @@
 - Verify denial and deactivation entries in a controlled test database; no Administrator sign-in is required</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>T-04, T-75, T-76</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Le Xin</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>E14 Audit &amp; History</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>E14-S03</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Read edited Activity log dates and times in Singapore time</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser or the assigned Event Coordinator, I want edited date/time values in my existing event Activity log to be readable in Singapore time so that I can understand the recorded edit without interpreting raw UTC strings.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Both existing readers see Singapore time
+Given an authorised Organiser or assigned Coordinator opens the existing event Activity log When an entry displays an edited date/time field value Then each date/time value already displayed by that view uses the existing shared Singapore formatter, including both old and new values where already shown, independently of the browser timezone; 2026-10-15T09:30:00Z represents 15 October 2026 at 17:30 Singapore time, not 16 October. Existing field keys are startAt, endAt and registrationDates; registrationDates stores "opensAt to closesAt", so both endpoints are formatted for display without changing that stored string.
+Scenario 2 - Singapore calendar rollover
+Given an edited date/time value is 2026-10-15T18:30:00Z When either view displays it Then it represents 16 October 2026 at 02:30 Singapore time; the calendar date as well as the hour is converted correctly.
+Scenario 3 - Missing and invalid values keep the existing contract
+Given a date/time value is missing or invalid When formatting is needed Then formatDate retains its existing "Not recorded" result; each view retains its existing omission/label-only behavior for absent change values, without throwing, inventing a date or introducing a new fallback.
+Scenario 4 - Other values and existing display paths unchanged
+Given an entry contains ordinary text, a status change or a venue hold expiry When either view renders it Then ordinary text remains text, existing status labels/badges remain unchanged, and existing hold-expiry formatting and behavior are preserved; the correction is field-aware, not conversion of every date-looking string.
+Scenario 5 - Audit evidence and access unchanged
+Given the existing event access rules apply When either permitted reader views or reloads the formatted log Then stored UTC old_value/new_value and occurred_at, actor and action remain unchanged and immutable; unauthorised readers remain refused and access-denial entries remain hidden from event logs, with no new audit viewer or permissions.
+Checklist
+- Scope implementation to the edited date/time value rendering in frontend/src/features/organiser/ClientEvents.tsx and frontend/src/features/events/ActivityLog.tsx using shared formatDate
+- Cover both views, same-day and rollover boundaries, missing/invalid inputs, other values and immutable/access-preserving reads with TC_E14S03_01 to _06
+- Do not add before/after history to a view that does not already show it; wider E14-S01 history remains separate
+- Exclude notification "Changed at ...Z" text, unrelated action/field labels, global viewers, new notifications and changes to stored audit data or hold-expiry behavior
+- Obtain human code/test review and future T-65/T-93 manual evidence; these planned cases are not execution evidence</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>T-93</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
@@ -3957,7 +4070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5380,25 +5493,72 @@
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>E03-S12</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Show consistent Organiser save success status</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser, I want confirmation of a saved event edit to use the shared success Alert so that I can recognise the same clear save outcome used on the Coordinator's event page.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Shared success Alert after a saved edit
+Given I may edit an event When a changed field saves successfully Then the event detail shows the existing field-specific saved message through the shared Alert with tone="success", retaining role="status" rather than replacing it with an urgent alert or plain paragraph.
+Scenario 2 - Saved data and audit survive reload
+Given an allowed event edit succeeds When the record reloads and I reopen it Then the changed value is retained and its existing activity-log entry remains available, with no extra save or audit write caused by rendering the confirmation.
+Scenario 3 - Failure cannot report success
+Given a new edit is invalid or its save request fails When I attempt to save Then the existing validation or error feedback remains and no success Alert claims that attempt was saved; starting a new edit clears the previous save confirmation.
+Scenario 4 - Cancellation and permissions unchanged
+Given I cancel an edit or attempt a field I cannot edit under the current event status and access rules When the attempt ends Then cancellation produces no save confirmation or mutation, and existing restrictions and change-request routing remain in force.
+Checklist
+- Reuse frontend/src/shared/feedback.tsx Alert in frontend/src/features/organiser/ClientEvents.tsx; preserve field-specific text and polite status semantics
+- Cover successful save/reload/audit, invalid input, failed request after a prior success, cancellation and restricted fields with TC_E03S12_01 to _05
+- Leave the Coordinator save flow, all other Organiser workflows, permissions and notifications unchanged; no redesign or new notification
+- Obtain human review of code and test cases and future manual evidence before claiming delivery; this definition does not execute those cases</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>T-93</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>E04-S01</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Record the event programme</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to record the programme for my event, including sessions and breaks, so that ConnectSphere can plan the venue and support around it.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Programme item added
 Given I am editing my event When I add a programme item with a title, start time and end time Then it appears in the event in chronological order
@@ -5408,39 +5568,39 @@
 Given two programme items overlap When I save them Then I am warned of the overlap</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>T-19</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>E04-S02</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Create a multi-session event</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to define an event made up of one or more Sessions so that each Session's requirements can be planned separately.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Sessions hold their own requirements
 Given I am creating an event When I add one or more Sessions Then each Session stores its date, time, expected attendance, venue requirements, and equipment requirements beneath the Event
@@ -5460,39 +5620,39 @@
 - Delete a Session and release its confirmed booking with notification and history</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>C-19, C-62, C-107, T-48, T-79, T-85</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>E05-S01</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Maintain the venue catalogue</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to add and update venue records so that Event Coordinators search against accurate information.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue added and searchable
 Given I am adding a venue When I save it with location, capacity, facilities, accessibility features, supported layouts and operating hours Then it becomes searchable by Event Coordinators
@@ -5511,39 +5671,39 @@
 - Be blocked from retiring a venue with future bookings, with those bookings identified</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>T-13, T-18, B-05</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>E05-S02</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Match layout requirements to venue capacity</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the room layouts supported by a venue and the maximum capacity for each layout, so that Event Coordinators only consider arrangements the venue can accommodate.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Layout and capacity stored
 Given I am editing a venue When I add a supported layout with its maximum capacity Then it is stored against that venue
@@ -5559,39 +5719,39 @@
 - Be warned when adding a layout that already exists</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>T-45, B-07</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E05-S03</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>View the venue availability calendar</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to view a venue's calendar so that I can see when the venue is free, pending, confirmed or blocked.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Four states distinguishable
 Given a venue has bookings and blocks in a period When I open its calendar for that period Then each entry is shown as Free, Tentative, Confirmed or Blocked, and the states are visually distinguishable
@@ -5608,39 +5768,39 @@
 - See periods I cannot view marked unavailable without any event detail</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>C-40, C-60, T-17, T-49</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>E05-S04</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Block a venue for maintenance</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to block a venue for maintenance, renovation or safety reasons so that it is not offered for events during that period.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Free period blocked
 Given a venue has no bookings in a period When I block that period and record a reason Then the venue no longer appears as available for those dates
@@ -5656,40 +5816,40 @@
 - Confirm affected Event Coordinators are notified when a block affects an upcoming event</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E05-S05</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Apply setup and turnaround time</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the setup and turnaround time each venue requires so that every availability and conflict check accounts for the time needed to prepare the room before an event and reset it afterwards.
 Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03, and Scenario 7 here rather than in E06-S01, because both of those stories are Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Buffers recorded on the venue
 Given I am creating or editing a venue When I enter a setup time and a turnaround time in whole minutes, either of which may be 0, and save Then both values are stored against the venue and shown on its detail, and every venue that existed before this story has both values at 0
@@ -5713,40 +5873,40 @@
 - Never have a booking released automatically because a buffer changed</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>C-65, T-66, T-73, T-74, O-20, O-21, O-22 (supersedes C-18, C-38)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mark a venue temporarily unavailable over existing bookings</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to mark a venue temporarily unavailable for maintenance, equipment failure, renovation, a safety concern or another operational reason, even when events are already booked in it, so that affected bookings are identified and their Coordinators can arrange an alternative without the events themselves being cancelled.
 New story from the Week 7 Customer Changes (C-66). It supersedes E05-S04 Scenario 2, which refused a block over a confirmed booking; E05-S04 is in the Sprint 2 sprint backlog and is not edited (T-67, T-74). Estimate to be set by planning poker at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Unavailability recorded with a reason
 Given I am viewing a venue When I mark it unavailable for a period and choose a reason category from maintenance, equipment failure, renovation, safety concern or other, with a free-text note Then the unavailability is saved with the period, the category, the note and my identity, and the calendar shows the period as Blocked
@@ -5770,37 +5930,37 @@
 - Confirm E05-S04's existing block, shorten and remove behaviour still works for periods with no bookings</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>C-66, C-48, C-61, T-28, T-67, T-74, O-23, O-24, O-25, O-26</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -5819,39 +5979,39 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>B-08</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -5880,39 +6040,39 @@
 - Identify outside operating hours as an advisory failure in E06-S02, without adding that rule to E06-S01</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-48 (supersedes T-21), T-77, B-08</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -5973,39 +6133,39 @@
 - Complete TC_E06S03_09 to _13 under the current Sprint 3 plan; record anything unfinished honestly at sprint close (PO confirmation, 16 October; T-94)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, T-78, O-27, O-29, O-30, T-94, T-95, T-96</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -6029,40 +6189,40 @@
 - Verify all three booking-log outcomes under TC_E06S04_05, TC_E06S04_06 and TC_E06S04_07</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66, T-75, T-76</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
 The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
@@ -6095,39 +6255,39 @@
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, T-78, T-92, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
@@ -6148,39 +6308,39 @@
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -6197,39 +6357,39 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -6245,39 +6405,39 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -6293,39 +6453,39 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -6344,39 +6504,39 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -6389,39 +6549,39 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -6437,39 +6597,39 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -6488,39 +6648,39 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E07-S08</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Link equipment requests and reservations to Sessions</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want equipment requests and reservations to identify the Session they support so that availability and fulfilment use the correct Session period.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request linked to its Session
 Given an Event has multiple Sessions When an Event Coordinator records equipment needed for one Session Then the request is linked to that Session and remains part of the Event
@@ -6537,37 +6697,37 @@
 - Keep technical-support staff assignment event-level</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-107, T-74, T-79</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E07-S09</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Preserve reservation warnings when stock reductions overlap withdrawals</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want catalogue stock reductions to account for dated equipment withdrawals so that reservations which no longer fit are flagged and their Coordinators are notified.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reduced usable stock flags reservations
 Given an item has total stock 10, four units withdrawn and five units reserved for the same future period When I reduce total stock to 8 Then the save succeeds, the reservation remains reserved but is marked for review, and its assigned active Coordinator receives one notification and an outbox record
@@ -6583,37 +6743,37 @@
 - Roll back stock, flags and notification/outbox writes together on failure</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E08-S01</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>View readiness of an event</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see whether venue, equipment and technical support are ready so that I know what still needs my attention.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Arrangement states shown
 Given an event is in planning When I open its readiness view Then each arrangement is shown as complete, in progress or not started
@@ -6621,39 +6781,39 @@
 Given an arrangement is not started When I view it Then the responsible role and the action required are shown</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>E08-S02</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Track outstanding actions across events</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a list of upcoming events with incomplete arrangements so that nothing is overlooked before an event takes place.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete events listed by date
 Given I have upcoming events with incomplete arrangements When I open my outstanding actions list Then those events are listed with the specific incomplete items, ordered by event date
@@ -6661,40 +6821,40 @@
 Given an event is close to its date and arrangements are still incomplete When I view the list Then that event is highlighted as urgent</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>C-28</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.
 Amended in place for the Week 7 Customer Changes (C-70, T-71; this story is To Do, T-74). Completing the arrangements no longer sets Confirmed directly: it lets the Coordinator submit the event for its Operational Safety Check, which moves it to the new Safety Review status, and the Safety Officer's approval (E08-S06) is what sets Confirmed. The readiness checks below are unchanged in substance; what they now gate is the submission. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event submitted for safety review
 Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, its full requested equipment is reserved and any requested technical support is assigned When I submit the event for its Operational Safety Check Then the status becomes Safety Review, the Safety Officer is notified, the Organiser is told the event is awaiting its safety check, and the event becomes Confirmed only when the Safety Officer approves it (E08-S06) (C-67, T-68, C-70, T-71; assumes O-28, O-39, O-40)
@@ -6720,39 +6880,39 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28, C-70, T-71, T-74, O-39, O-40</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a confirmed event to return to Planning when an arrangement requires it so that the system reflects the event's readiness and starts safety review at the right time.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Manual reversion records a reason
 Given an event is Confirmed When I deliberately revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -6773,39 +6933,39 @@
 - Retain earlier safety decisions in history without reusing them</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28, C-70, T-71, C-120, T-81, C-132, T-82</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -6823,40 +6983,40 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>E08-S06</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Conduct the Operational Safety Check as the Safety Officer</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>As a Safety Officer, I want to review the operational safety of each event whose venue and technical arrangements are confirmed, and approve it, reject its safety arrangement or request changes, so that no event proceeds to preparation until it is safe to run.
 New story from the Week 7 Customer Changes (C-70) and the seventh role (T-72). The Safety Review status it works on sits between Planning and Confirmed as an interim placement (T-71); O-39 asks the customer to confirm. The customer guarantees a response, so there is no timeout path. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events awaiting review listed with what the check needs
 Given events are in Safety Review When I open my queue Then each shows the event name, date and time, every confirmed venue with its capacity, layout and known restrictions, expected attendance, accessibility requirements, equipment and its placement, and the time it entered Safety Review, oldest first
@@ -6889,37 +7049,37 @@
 - Confirm every decision is in the activity log</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>C-70, T-71, T-72, T-73, T-74, O-39, O-40, O-41, O-42, O-43</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register once for a confirmed Event and select the Sessions I will attend so that my place is reserved across the Event I chose.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open Event
 Given an Event is Confirmed, registration is open, and selected Sessions have capacity When I submit the required registration information and select one or more Sessions Then one active Event-level registration records those Sessions and I receive a confirmation with the Event and selected Session details
@@ -6940,39 +7100,39 @@
 - See the primary Event venue and the venue for each selected Session</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>C-35, C-67, C-97, C-107, T-68, T-78, T-79, T-85</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want the system to enforce each selected Session's approved layout capacity and the combined Event capacity so that registrations do not exceed either limit.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Both capacity limits enforced
 Given a registration selects one or more Sessions When the request is within each selected Session's approved layout capacity and within the combined Event capacity Then it may be confirmed; if either limit would be exceeded it is not confirmed as an approved seat (C-78, T-85)
@@ -6998,39 +7158,39 @@
 - Allow manual VIP additions only within both limits and block them at either limit</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, C-78, C-98, T-30, T-31, T-50, T-85, B-11, O-50</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set one registration and withdrawal window for the Event so that attendees can select Sessions within a consistent Event-level period.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the Event-level registration opening date has not been reached When an Attendee views the Event Then registration is shown as not yet open and the opening date is stated
@@ -7049,39 +7209,39 @@
 - Warn when the closing date is after the Event has started</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42, T-79, T-85</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given the combined Event capacity is full and its Event-level waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released (Session-specific waiting-list behavior remains open under O-50)
@@ -7100,39 +7260,39 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10, O-50</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my Event registration so that my Event place and places in all selected Sessions are released together.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn from Event and Sessions
 Given I have an active Event registration selecting one or more Sessions and the withdrawal deadline has not passed When I withdraw Then the Event registration is cancelled and its approved places are released from every selected Session and from the combined Event capacity
@@ -7144,39 +7304,39 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10, T-79, T-85</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -7192,39 +7352,39 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -7242,39 +7402,39 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my Event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the Event
@@ -7296,39 +7456,39 @@
 - Confirm Pending requests become Obsolete with history when the Event becomes Completed or Cancelled</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G67" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, C-77, T-16, T-88</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to identify which Session arrangements a change affects so that I re-check the right bookings and reservations.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Session attendance beyond capacity flagged
 Given a Session has a confirmed venue booking When its expected attendance changes Then each booking whose own headcount is set uses that headcount, otherwise it uses the Session attendance; only a booking whose governing headcount exceeds capacity is flagged and Venue Staff are notified
@@ -7351,39 +7511,39 @@
 - Notify staff responsible for the affected arrangements</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G68" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27, C-107, T-79</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>E10-S03</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Reschedule an event</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to reschedule an Event while identifying the Session arrangements that must be reconfirmed so that it can still take place when the original dates no longer work.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Session date change flags its arrangements
 Given an Event has confirmed Session venue bookings or equipment reservations When I change one Session's date or time Then only that Session's existing arrangements are flagged for reconfirmation and are not moved silently
@@ -7400,39 +7560,39 @@
 - Close Pending change requests as Obsolete when the Event becomes Completed or Cancelled</t>
         </is>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>C-25, O-18, C-77, C-107, T-79, T-88</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr"/>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an Event and release its Session arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled and Session arrangements released
 Given an Event Organiser requests cancellation When I cancel the Event and record a reason Then its status becomes Cancelled, all Session venue bookings and equipment reservations are released, calendars/availability are updated, and affected staff are notified
@@ -7453,40 +7613,40 @@
 - Close Pending change requests as Obsolete with history</t>
         </is>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G70" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, C-77, T-07, T-48, T-79, T-88</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr"/>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>E10-S05</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Handle a venue lost from a confirmed event</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
 Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Lost venue flags the event
 Given my event has a Pending or Confirmed venue booking When Venue Staff mark that venue unavailable over the booking's period (E05-S06) Then I am notified, the booking shows as Conflicting on the event, and the event is flagged as needing alternative arrangements while its status and every other arrangement stay as they were (assumes O-24)
@@ -7504,39 +7664,39 @@
 - Confirm the Organiser and registered Attendees are told of the venue change only when it actually happens</t>
         </is>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G71" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>C-66, C-61, T-28, T-67, T-73, T-74, O-24, O-25</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr"/>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -7564,39 +7724,39 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70, C-70, T-71</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr"/>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>E11-S03</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Receive reminders about upcoming commitments</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want reminders about upcoming events I am supporting so that equipment and support are prepared in time.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reminder lists requirements
 Given I am assigned to an upcoming event When the reminder point before it is reached Then I receive a reminder listing the equipment and support required
@@ -7604,39 +7764,39 @@
 Given an event is cancelled before its reminder is due When the reminder point is reached Then no reminder is sent</t>
         </is>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>C-28, O-11</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr"/>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>E11-S04</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Alert on incomplete arrangements</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when an upcoming event still has incomplete arrangements so that I can act while there is still time.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete items named
 Given an upcoming event has an incomplete essential arrangement When the alert point before it is reached Then I receive an alert naming the incomplete items
@@ -7644,39 +7804,39 @@
 Given all arrangements are completed before the alert point When the alert point is reached Then no alert is sent</t>
         </is>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="G74" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr"/>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>E12-S01</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>View my events in a calendar</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see my events in a calendar so that I can plan my workload across the coming weeks.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events shown on their dates
 Given I have events spread across several weeks When I open the calendar Then my events appear on their dates with their status indicated
@@ -7684,39 +7844,39 @@
 Given an event spans several days When I view the calendar Then it is shown across all its days rather than only the first</t>
         </is>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="G75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr"/>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>E12-S02</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Search and filter events</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search events by name, client, date, venue, status, category or assigned Coordinator so that I can find a specific event quickly.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Permitted matches returned
 Given events match my criteria When I search Then only matching events that I am permitted to see are returned
@@ -7726,39 +7886,39 @@
 Given I apply several filters at once When I search Then all the filters are applied together</t>
         </is>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="G76" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr"/>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>E12-S03</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>See my work on a role-based dashboard</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want a dashboard showing booking requests awaiting my decision and upcoming venue preparations so that I can see my outstanding work in one place.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Pending decisions listed
 Given booking requests are pending my decision When I open my dashboard Then they are listed with event name, venue, dates and how long each has been waiting
@@ -7766,39 +7926,39 @@
 Given I have no outstanding items When I open my dashboard Then an empty state is shown rather than an error</t>
         </is>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="G77" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr"/>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>E12-S04</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Use the system on a mobile device</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to use the system on my phone while preparing a venue so that I can check and update arrangements without returning to a desk.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Readable without horizontal scrolling
 Given I open the system on a mobile device When I view my dashboard, an event or a venue calendar Then the content is readable and usable without horizontal scrolling
@@ -7806,39 +7966,39 @@
 Given I am working on a mobile device When I update a preparation status Then the update is saved exactly as it would be on a desktop</t>
         </is>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="G78" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr"/>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>E13-S01</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Generate an event report</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to generate a summary report for an event so that I can share the arrangements at operational meetings.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Generate a downloadable report containing event name, date and time, venue, equipment list, assigned technical support and total registered Attendees
@@ -7847,39 +8007,39 @@
 - Show a clear error with a retry option if generation fails</t>
         </is>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="G79" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr"/>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>E13-S02</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Review venue usage over a period</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to review venue bookings and usage over a chosen period so that I can plan maintenance and identify under-used spaces.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Select a custom date range with start and end dates
@@ -7889,39 +8049,39 @@
 - See an informative empty state when no records match</t>
         </is>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="G80" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr"/>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>E13-S03</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Export attendee registration information</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to export the registration list for my event so that I can prepare badges and catering numbers.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Export registrations only for events the Organiser manages
@@ -7929,39 +8089,39 @@
 - Exclude sensitive personal data from the generated file</t>
         </is>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="G81" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr"/>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>E14-S01</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>View an event's change history</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see how an event's important information has changed over time so that I can explain how the current arrangements were reached.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before and after values listed
 Given an event's date, venue, attendance or status has changed When I open its change history Then each change is listed with the previous value, the new value, who made it and when
@@ -7969,39 +8129,39 @@
 Given I am not permitted to view a particular change When I open the history Then that entry is not shown to me</t>
         </is>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="G82" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr"/>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log; access-denial entries are not shown in that log
@@ -8023,15 +8183,65 @@
 - Verify denial and deactivation entries in a controlled test database; no Administrator sign-in is required</t>
         </is>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="G83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>T-04, T-75, T-76</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>E14 Audit &amp; History</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>E14-S03</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Read edited Activity log dates and times in Singapore time</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser or the assigned Event Coordinator, I want edited date/time values in my existing event Activity log to be readable in Singapore time so that I can understand the recorded edit without interpreting raw UTC strings.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Both existing readers see Singapore time
+Given an authorised Organiser or assigned Coordinator opens the existing event Activity log When an entry displays an edited date/time field value Then each date/time value already displayed by that view uses the existing shared Singapore formatter, including both old and new values where already shown, independently of the browser timezone; 2026-10-15T09:30:00Z represents 15 October 2026 at 17:30 Singapore time, not 16 October. Existing field keys are startAt, endAt and registrationDates; registrationDates stores "opensAt to closesAt", so both endpoints are formatted for display without changing that stored string.
+Scenario 2 - Singapore calendar rollover
+Given an edited date/time value is 2026-10-15T18:30:00Z When either view displays it Then it represents 16 October 2026 at 02:30 Singapore time; the calendar date as well as the hour is converted correctly.
+Scenario 3 - Missing and invalid values keep the existing contract
+Given a date/time value is missing or invalid When formatting is needed Then formatDate retains its existing "Not recorded" result; each view retains its existing omission/label-only behavior for absent change values, without throwing, inventing a date or introducing a new fallback.
+Scenario 4 - Other values and existing display paths unchanged
+Given an entry contains ordinary text, a status change or a venue hold expiry When either view renders it Then ordinary text remains text, existing status labels/badges remain unchanged, and existing hold-expiry formatting and behavior are preserved; the correction is field-aware, not conversion of every date-looking string.
+Scenario 5 - Audit evidence and access unchanged
+Given the existing event access rules apply When either permitted reader views or reloads the formatted log Then stored UTC old_value/new_value and occurred_at, actor and action remain unchanged and immutable; unauthorised readers remain refused and access-denial entries remain hidden from event logs, with no new audit viewer or permissions.
+Checklist
+- Scope implementation to the edited date/time value rendering in frontend/src/features/organiser/ClientEvents.tsx and frontend/src/features/events/ActivityLog.tsx using shared formatDate
+- Cover both views, same-day and rollover boundaries, missing/invalid inputs, other values and immutable/access-preserving reads with TC_E14S03_01 to _06
+- Do not add before/after history to a view that does not already show it; wider E14-S01 history remains separate
+- Exclude notification "Changed at ...Z" text, unrelated action/field labels, global viewers, new notifications and changes to stored audit data or hold-expiry behavior
+- Obtain human code/test review and future T-65/T-93 manual evidence; these planned cases are not execution evidence</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>T-93</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 161026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 161026.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1718,20 +1718,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>E03-S11</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Let the Organiser edit registration setup and fix the date layout</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser, I want to fill in and correct the registration setup on my event request, and read the registration dates clearly, so that a request that left the registration setup blank can still be completed for approval.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Organiser edits registration setup before approval
+Given my event has not yet been approved When I edit its registration setup Then the change is saved against the event and recorded in the activity log
+Scenario 2 - Registration setup cannot be cleared
+Given my event has a registration setup When I try to save it empty Then the save is blocked and the recorded registration setup is unchanged
+Scenario 3 - Registration setup restricted for the Organiser after approval
+Given my event has been approved When I open its edit form Then the registration setup is read-only and I am directed to raise a change request (E10-S01)
+Scenario 4 - Coordinator edits registration setup after approval
+Given an event has been approved When I edit its registration setup as the assigned Coordinator Then the change is saved and recorded in the activity log
+Scenario 5 - Registration dates laid out clearly
+Given I am editing an event When I view the Registration section Then "Registration opens" and "Registration closes" are shown as two separate labelled fields, each label with its own input, with no sideways scrolling at phone width
+Checklist
+- Edit the registration setup as the Organiser before approval, with the edit recorded in the activity log
+- Be blocked when saving an empty registration setup
+- See the registration setup read-only after approval, with a link to request a change
+- Edit the registration setup as the assigned Coordinator after approval, with the edit recorded in the activity log
+- See "Registration opens" and "Registration closes" as two labelled fields at desktop and phone width</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>C-52, T-16, T-74</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
           <t>E03-S12</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Show consistent Organiser save success status</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want confirmation of a saved event edit to use the shared success Alert so that I can recognise the same clear save outcome used on the Coordinator's event page.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Shared success Alert after a saved edit
 Given I may edit an event When a changed field saves successfully Then the event detail shows the existing field-specific saved message through the shared Alert with tone="success", retaining role="status" rather than replacing it with an urgent alert or plain paragraph.
@@ -1748,41 +1802,41 @@
 - Obtain human review of code and test cases and future manual evidence before claiming delivery; this definition does not execute those cases</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>T-93</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>T-97</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>E04-S02</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Create a multi-session event</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to define an event made up of one or more Sessions so that each Session's requirements can be planned separately.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Sessions hold their own requirements
 Given I am creating an event When I add one or more Sessions Then each Session stores its date, time, expected attendance, venue requirements, and equipment requirements beneath the Event
@@ -1802,43 +1856,43 @@
 - Delete a Session and release its confirmed booking with notification and history</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>C-19, C-62, C-107, T-48, T-79, T-85</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>E05-S01</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Maintain the venue catalogue</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to add and update venue records so that Event Coordinators search against accurate information.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue added and searchable
 Given I am adding a venue When I save it with location, capacity, facilities, accessibility features, supported layouts and operating hours Then it becomes searchable by Event Coordinators
@@ -1857,47 +1911,47 @@
 - Be blocked from retiring a venue with future bookings, with those bookings identified</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>T-13, T-18, B-05</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>E05-S02</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Match layout requirements to venue capacity</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the room layouts supported by a venue and the maximum capacity for each layout, so that Event Coordinators only consider arrangements the venue can accommodate.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Layout and capacity stored
 Given I am editing a venue When I add a supported layout with its maximum capacity Then it is stored against that venue
@@ -1913,47 +1967,47 @@
 - Be warned when adding a layout that already exists</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>T-45, B-07</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>E05-S03</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>View the venue availability calendar</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to view a venue's calendar so that I can see when the venue is free, pending, confirmed or blocked.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Four states distinguishable
 Given a venue has bookings and blocks in a period When I open its calendar for that period Then each entry is shown as Free, Tentative, Confirmed or Blocked, and the states are visually distinguishable
@@ -1970,43 +2024,43 @@
 - See periods I cannot view marked unavailable without any event detail</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>C-40, C-60, T-17, T-49</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>E05-S04</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Block a venue for maintenance</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to block a venue for maintenance, renovation or safety reasons so that it is not offered for events during that period.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Free period blocked
 Given a venue has no bookings in a period When I block that period and record a reason Then the venue no longer appears as available for those dates
@@ -2022,44 +2076,44 @@
 - Confirm affected Event Coordinators are notified when a block affects an upcoming event</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>E05-S05</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Apply setup and turnaround time</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the setup and turnaround time each venue requires so that every availability and conflict check accounts for the time needed to prepare the room before an event and reset it afterwards.
 Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03, and Scenario 7 here rather than in E06-S01, because both of those stories are Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Buffers recorded on the venue
 Given I am creating or editing a venue When I enter a setup time and a turnaround time in whole minutes, either of which may be 0, and save Then both values are stored against the venue and shown on its detail, and every venue that existed before this story has both values at 0
@@ -2083,44 +2137,44 @@
 - Never have a booking released automatically because a buffer changed</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>C-65, T-66, T-73, T-74, O-20, O-21, O-22 (supersedes C-18, C-38)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mark a venue temporarily unavailable over existing bookings</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to mark a venue temporarily unavailable for maintenance, equipment failure, renovation, a safety concern or another operational reason, even when events are already booked in it, so that affected bookings are identified and their Coordinators can arrange an alternative without the events themselves being cancelled.
 New story from the Week 7 Customer Changes (C-66). It supersedes E05-S04 Scenario 2, which refused a block over a confirmed booking; E05-S04 is in the Sprint 2 sprint backlog and is not edited (T-67, T-74). Estimate to be set by planning poker at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Unavailability recorded with a reason
 Given I am viewing a venue When I mark it unavailable for a period and choose a reason category from maintenance, equipment failure, renovation, safety concern or other, with a free-text note Then the unavailability is saved with the period, the category, the note and my identity, and the calendar shows the period as Blocked
@@ -2144,41 +2198,41 @@
 - Confirm E05-S04's existing block, shorten and remove behaviour still works for periods with no bookings</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>C-66, C-48, C-61, T-28, T-67, T-74, O-23, O-24, O-25, O-26</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -2197,43 +2251,43 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>B-08</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -2262,43 +2316,43 @@
 - Identify outside operating hours as an advisory failure in E06-S02, without adding that rule to E06-S01</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-48 (supersedes T-21), T-77, B-08</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -2359,43 +2413,43 @@
 - Complete TC_E06S03_09 to _13 under the current Sprint 3 plan; record anything unfinished honestly at sprint close (PO confirmation, 16 October; T-94)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, T-78, O-27, O-29, O-30, T-94, T-95, T-96</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -2419,48 +2473,48 @@
 - Verify all three booking-log outcomes under TC_E06S04_05, TC_E06S04_06 and TC_E06S04_07</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66, T-75, T-76</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
 The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
@@ -2493,100 +2547,101 @@
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, T-78, T-92, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
-Scenario 2 - Competing request flagged
-Given two pending requests cover the same venue and overlapping times When I approve one of them Then the other is flagged as conflicting and cannot be approved until the conflict is resolved
+Scenario 2 - Buffer change flags a retained request conflict
+Given booking A for 10:00-12:00 is Confirmed and request B for 12:30-14:00 is Pending on the same venue and day, both created with zero setup and turnaround buffers When Venue Staff change setup to 30 minutes and turnaround to 45 minutes Then their half-open occupied windows `[start - setup, end + turnaround)` become A `[09:30,12:45)` and B `[12:00,14:45)`, B is flagged `buffer_conflict` without changing its lifecycle status to Conflicting, and a Venue Staff attempt to approve B is blocked with A identified as the conflict; A remains Confirmed, B remains Pending, and both retain occupancy until the conflict is resolved
 Scenario 3 - Simultaneous approval fails safely
 Given another Venue Staff member approves a conflicting request moments before me When my approval is processed Then it fails and I am told the venue has just been taken
-Scenario 4 - Buffered windows are what must not overlap
-Given two pending requests on one venue whose advertised times do not overlap but whose buffered occupancy windows do When both are approved at the same moment Then at most one approval succeeds and the other fails safely, because the database-level conflict check operates on the buffered window (C-65, T-66, ADR-003)
+Scenario 4 - Simultaneous submissions enforce buffered occupancy
+Given a free venue has setup 30 minutes and turnaround 45 minutes and assigned Coordinators prepare requests for 10:00-12:00 and 12:30-14:00 on the same day When both requests are submitted simultaneously Then at most one Pending row is created and the losing submission fails safely with a conflict, because the half-open occupied windows `[start - setup, end + turnaround)` are `[09:30,12:45)` and `[12:00,14:45)` and overlap; the database guard checks buffered occupancy at submission, and no approval is performed (C-65, T-66, ADR-003)
 Scenario 5 - Conflicts are per venue, not per event
 Given one event has Pending requests on two different venues over the same period When both are approved Then both become Confirmed, because double-booking is detected per venue and an event may legitimately occupy several venues at once (C-67, T-68)
 Checklist
 - Be blocked from approving a request overlapping an existing confirmed booking
 - See which existing booking is causing the conflict
-- Confirm a competing pending request is flagged as conflicting once one is approved
+- Confirm a buffer edit flags B with `buffer_conflict`, blocks its approval with A identified, and retains A as Confirmed and B as Pending with both still occupying
+- Confirm simultaneous submissions with overlapping buffered windows create at most one Pending row and return a safe conflict to the loser without approving either
 - Confirm a simultaneous approval by another Venue Staff member fails safely
 - Be told the venue has been taken when a simultaneous approval wins
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -2603,43 +2658,43 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -2655,43 +2710,43 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -2707,43 +2762,43 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -2762,43 +2817,43 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -2811,43 +2866,43 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -2863,43 +2918,43 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -2918,39 +2973,39 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E07-S08</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Link equipment requests and reservations to Sessions</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want equipment requests and reservations to identify the Session they support so that availability and fulfilment use the correct Session period.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request linked to its Session
 Given an Event has multiple Sessions When an Event Coordinator records equipment needed for one Session Then the request is linked to that Session and remains part of the Event
@@ -2967,37 +3022,37 @@
 - Keep technical-support staff assignment event-level</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>C-107, T-74, T-79</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E07-S09</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Preserve reservation warnings when stock reductions overlap withdrawals</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want catalogue stock reductions to account for dated equipment withdrawals so that reservations which no longer fit are flagged and their Coordinators are notified.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reduced usable stock flags reservations
 Given an item has total stock 10, four units withdrawn and five units reserved for the same future period When I reduce total stock to 8 Then the save succeeds, the reservation remains reserved but is marked for review, and its assigned active Coordinator receives one notification and an outbox record
@@ -3013,42 +3068,42 @@
 - Roll back stock, flags and notification/outbox writes together on failure</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.
 Amended in place for the Week 7 Customer Changes (C-70, T-71; this story is To Do, T-74). Completing the arrangements no longer sets Confirmed directly: it lets the Coordinator submit the event for its Operational Safety Check, which moves it to the new Safety Review status, and the Safety Officer's approval (E08-S06) is what sets Confirmed. The readiness checks below are unchanged in substance; what they now gate is the submission. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event submitted for safety review
 Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, its full requested equipment is reserved and any requested technical support is assigned When I submit the event for its Operational Safety Check Then the status becomes Safety Review, the Safety Officer is notified, the Organiser is told the event is awaiting its safety check, and the event becomes Confirmed only when the Safety Officer approves it (E08-S06) (C-67, T-68, C-70, T-71; assumes O-28, O-39, O-40)
@@ -3074,43 +3129,43 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28, C-70, T-71, T-74, O-39, O-40</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a confirmed event to return to Planning when an arrangement requires it so that the system reflects the event's readiness and starts safety review at the right time.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Manual reversion records a reason
 Given an event is Confirmed When I deliberately revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -3131,43 +3186,43 @@
 - Retain earlier safety decisions in history without reusing them</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28, C-70, T-71, C-120, T-81, C-132, T-82</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -3185,44 +3240,44 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E08-S06</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Conduct the Operational Safety Check as the Safety Officer</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As a Safety Officer, I want to review the operational safety of each event whose venue and technical arrangements are confirmed, and approve it, reject its safety arrangement or request changes, so that no event proceeds to preparation until it is safe to run.
 New story from the Week 7 Customer Changes (C-70) and the seventh role (T-72). The Safety Review status it works on sits between Planning and Confirmed as an interim placement (T-71); O-39 asks the customer to confirm. The customer guarantees a response, so there is no timeout path. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events awaiting review listed with what the check needs
 Given events are in Safety Review When I open my queue Then each shows the event name, date and time, every confirmed venue with its capacity, layout and known restrictions, expected attendance, accessibility requirements, equipment and its placement, and the time it entered Safety Review, oldest first
@@ -3255,41 +3310,41 @@
 - Confirm every decision is in the activity log</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-70, T-71, T-72, T-73, T-74, O-39, O-40, O-41, O-42, O-43</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register once for a confirmed Event and select the Sessions I will attend so that my place is reserved across the Event I chose.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open Event
 Given an Event is Confirmed, registration is open, and selected Sessions have capacity When I submit the required registration information and select one or more Sessions Then one active Event-level registration records those Sessions and I receive a confirmation with the Event and selected Session details
@@ -3310,43 +3365,43 @@
 - See the primary Event venue and the venue for each selected Session</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-35, C-67, C-97, C-107, T-68, T-78, T-79, T-85</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want the system to enforce each selected Session's approved layout capacity and the combined Event capacity so that registrations do not exceed either limit.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Both capacity limits enforced
 Given a registration selects one or more Sessions When the request is within each selected Session's approved layout capacity and within the combined Event capacity Then it may be confirmed; if either limit would be exceeded it is not confirmed as an approved seat (C-78, T-85)
@@ -3372,43 +3427,43 @@
 - Allow manual VIP additions only within both limits and block them at either limit</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, C-78, C-98, T-30, T-31, T-50, T-85, B-11, O-50</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set one registration and withdrawal window for the Event so that attendees can select Sessions within a consistent Event-level period.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the Event-level registration opening date has not been reached When an Attendee views the Event Then registration is shown as not yet open and the opening date is stated
@@ -3427,43 +3482,43 @@
 - Warn when the closing date is after the Event has started</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42, T-79, T-85</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given the combined Event capacity is full and its Event-level waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released (Session-specific waiting-list behavior remains open under O-50)
@@ -3482,43 +3537,43 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10, O-50</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my Event registration so that my Event place and places in all selected Sessions are released together.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn from Event and Sessions
 Given I have an active Event registration selecting one or more Sessions and the withdrawal deadline has not passed When I withdraw Then the Event registration is cancelled and its approved places are released from every selected Session and from the combined Event capacity
@@ -3530,43 +3585,43 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10, T-79, T-85</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -3582,43 +3637,43 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -3636,43 +3691,43 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my Event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the Event
@@ -3694,43 +3749,43 @@
 - Confirm Pending requests become Obsolete with history when the Event becomes Completed or Cancelled</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, C-77, T-16, T-88</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to identify which Session arrangements a change affects so that I re-check the right bookings and reservations.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Session attendance beyond capacity flagged
 Given a Session has a confirmed venue booking When its expected attendance changes Then each booking whose own headcount is set uses that headcount, otherwise it uses the Session attendance; only a booking whose governing headcount exceeds capacity is flagged and Venue Staff are notified
@@ -3753,43 +3808,43 @@
 - Notify staff responsible for the affected arrangements</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27, C-107, T-79</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an Event and release its Session arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled and Session arrangements released
 Given an Event Organiser requests cancellation When I cancel the Event and record a reason Then its status becomes Cancelled, all Session venue bookings and equipment reservations are released, calendars/availability are updated, and affected staff are notified
@@ -3810,44 +3865,44 @@
 - Close Pending change requests as Obsolete with history</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, C-77, T-07, T-48, T-79, T-88</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>E10-S05</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Handle a venue lost from a confirmed event</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
 Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Lost venue flags the event
 Given my event has a Pending or Confirmed venue booking When Venue Staff mark that venue unavailable over the booking's period (E05-S06) Then I am notified, the booking shows as Conflicting on the event, and the event is flagged as needing alternative arrangements while its status and every other arrangement stay as they were (assumes O-24)
@@ -3865,43 +3920,43 @@
 - Confirm the Organiser and registered Attendees are told of the venue change only when it actually happens</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>C-66, C-61, T-28, T-67, T-73, T-74, O-24, O-25</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -3929,43 +3984,43 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70, C-70, T-71</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log; access-denial entries are not shown in that log
@@ -3987,47 +4042,47 @@
 - Verify denial and deactivation entries in a controlled test database; no Administrator sign-in is required</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>T-04, T-75, T-76</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>E14-S03</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Read edited Activity log dates and times in Singapore time</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser or the assigned Event Coordinator, I want edited date/time values in my existing event Activity log to be readable in Singapore time so that I can understand the recorded edit without interpreting raw UTC strings.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Both existing readers see Singapore time
 Given an authorised Organiser or assigned Coordinator opens the existing event Activity log When an entry displays an edited date/time field value Then each date/time value already displayed by that view uses the existing shared Singapore formatter, including both old and new values where already shown, independently of the browser timezone; 2026-10-15T09:30:00Z represents 15 October 2026 at 17:30 Singapore time, not 16 October. Existing field keys are startAt, endAt and registrationDates; registrationDates stores "opensAt to closesAt", so both endpoints are formatted for display without changing that stored string.
@@ -4047,13 +4102,13 @@
 - Obtain human code/test review and future T-65/T-93 manual evidence; these planned cases are not execution evidence</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>T-93</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>T-97</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
@@ -4070,7 +4125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5498,20 +5553,70 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>E03-S11</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Let the Organiser edit registration setup and fix the date layout</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser, I want to fill in and correct the registration setup on my event request, and read the registration dates clearly, so that a request that left the registration setup blank can still be completed for approval.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Organiser edits registration setup before approval
+Given my event has not yet been approved When I edit its registration setup Then the change is saved against the event and recorded in the activity log
+Scenario 2 - Registration setup cannot be cleared
+Given my event has a registration setup When I try to save it empty Then the save is blocked and the recorded registration setup is unchanged
+Scenario 3 - Registration setup restricted for the Organiser after approval
+Given my event has been approved When I open its edit form Then the registration setup is read-only and I am directed to raise a change request (E10-S01)
+Scenario 4 - Coordinator edits registration setup after approval
+Given an event has been approved When I edit its registration setup as the assigned Coordinator Then the change is saved and recorded in the activity log
+Scenario 5 - Registration dates laid out clearly
+Given I am editing an event When I view the Registration section Then "Registration opens" and "Registration closes" are shown as two separate labelled fields, each label with its own input, with no sideways scrolling at phone width
+Checklist
+- Edit the registration setup as the Organiser before approval, with the edit recorded in the activity log
+- Be blocked when saving an empty registration setup
+- See the registration setup read-only after approval, with a link to request a change
+- Edit the registration setup as the assigned Coordinator after approval, with the edit recorded in the activity log
+- See "Registration opens" and "Registration closes" as two labelled fields at desktop and phone width</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>C-52, T-16, T-74</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
           <t>E03-S12</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Show consistent Organiser save success status</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want confirmation of a saved event edit to use the shared success Alert so that I can recognise the same clear save outcome used on the Coordinator's event page.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Shared success Alert after a saved edit
 Given I may edit an event When a changed field saves successfully Then the event detail shows the existing field-specific saved message through the shared Alert with tone="success", retaining role="status" rather than replacing it with an urgent alert or plain paragraph.
@@ -5528,37 +5633,37 @@
 - Obtain human review of code and test cases and future manual evidence before claiming delivery; this definition does not execute those cases</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>T-93</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>T-97</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>E04-S01</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Record the event programme</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to record the programme for my event, including sessions and breaks, so that ConnectSphere can plan the venue and support around it.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Programme item added
 Given I am editing my event When I add a programme item with a title, start time and end time Then it appears in the event in chronological order
@@ -5568,39 +5673,39 @@
 Given two programme items overlap When I save them Then I am warned of the overlap</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>T-19</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>E04-S02</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Create a multi-session event</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to define an event made up of one or more Sessions so that each Session's requirements can be planned separately.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Sessions hold their own requirements
 Given I am creating an event When I add one or more Sessions Then each Session stores its date, time, expected attendance, venue requirements, and equipment requirements beneath the Event
@@ -5620,39 +5725,39 @@
 - Delete a Session and release its confirmed booking with notification and history</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>C-19, C-62, C-107, T-48, T-79, T-85</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>E05-S01</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Maintain the venue catalogue</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to add and update venue records so that Event Coordinators search against accurate information.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue added and searchable
 Given I am adding a venue When I save it with location, capacity, facilities, accessibility features, supported layouts and operating hours Then it becomes searchable by Event Coordinators
@@ -5671,39 +5776,39 @@
 - Be blocked from retiring a venue with future bookings, with those bookings identified</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>T-13, T-18, B-05</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E05-S02</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Match layout requirements to venue capacity</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the room layouts supported by a venue and the maximum capacity for each layout, so that Event Coordinators only consider arrangements the venue can accommodate.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Layout and capacity stored
 Given I am editing a venue When I add a supported layout with its maximum capacity Then it is stored against that venue
@@ -5719,39 +5824,39 @@
 - Be warned when adding a layout that already exists</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>T-45, B-07</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>E05-S03</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>View the venue availability calendar</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to view a venue's calendar so that I can see when the venue is free, pending, confirmed or blocked.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Four states distinguishable
 Given a venue has bookings and blocks in a period When I open its calendar for that period Then each entry is shown as Free, Tentative, Confirmed or Blocked, and the states are visually distinguishable
@@ -5768,39 +5873,39 @@
 - See periods I cannot view marked unavailable without any event detail</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>C-40, C-60, T-17, T-49</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E05-S04</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Block a venue for maintenance</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to block a venue for maintenance, renovation or safety reasons so that it is not offered for events during that period.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Free period blocked
 Given a venue has no bookings in a period When I block that period and record a reason Then the venue no longer appears as available for those dates
@@ -5816,40 +5921,40 @@
 - Confirm affected Event Coordinators are notified when a block affects an upcoming event</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E05-S05</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Apply setup and turnaround time</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the setup and turnaround time each venue requires so that every availability and conflict check accounts for the time needed to prepare the room before an event and reset it afterwards.
 Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03, and Scenario 7 here rather than in E06-S01, because both of those stories are Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Buffers recorded on the venue
 Given I am creating or editing a venue When I enter a setup time and a turnaround time in whole minutes, either of which may be 0, and save Then both values are stored against the venue and shown on its detail, and every venue that existed before this story has both values at 0
@@ -5873,40 +5978,40 @@
 - Never have a booking released automatically because a buffer changed</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>C-65, T-66, T-73, T-74, O-20, O-21, O-22 (supersedes C-18, C-38)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mark a venue temporarily unavailable over existing bookings</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to mark a venue temporarily unavailable for maintenance, equipment failure, renovation, a safety concern or another operational reason, even when events are already booked in it, so that affected bookings are identified and their Coordinators can arrange an alternative without the events themselves being cancelled.
 New story from the Week 7 Customer Changes (C-66). It supersedes E05-S04 Scenario 2, which refused a block over a confirmed booking; E05-S04 is in the Sprint 2 sprint backlog and is not edited (T-67, T-74). Estimate to be set by planning poker at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Unavailability recorded with a reason
 Given I am viewing a venue When I mark it unavailable for a period and choose a reason category from maintenance, equipment failure, renovation, safety concern or other, with a free-text note Then the unavailability is saved with the period, the category, the note and my identity, and the calendar shows the period as Blocked
@@ -5930,37 +6035,37 @@
 - Confirm E05-S04's existing block, shorten and remove behaviour still works for periods with no bookings</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>C-66, C-48, C-61, T-28, T-67, T-74, O-23, O-24, O-25, O-26</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -5979,39 +6084,39 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>B-08</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -6040,39 +6145,39 @@
 - Identify outside operating hours as an advisory failure in E06-S02, without adding that rule to E06-S01</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-48 (supersedes T-21), T-77, B-08</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -6133,39 +6238,39 @@
 - Complete TC_E06S03_09 to _13 under the current Sprint 3 plan; record anything unfinished honestly at sprint close (PO confirmation, 16 October; T-94)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, T-78, O-27, O-29, O-30, T-94, T-95, T-96</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -6189,40 +6294,40 @@
 - Verify all three booking-log outcomes under TC_E06S04_05, TC_E06S04_06 and TC_E06S04_07</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66, T-75, T-76</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
 The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
@@ -6255,92 +6360,93 @@
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, T-78, T-92, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
-Scenario 2 - Competing request flagged
-Given two pending requests cover the same venue and overlapping times When I approve one of them Then the other is flagged as conflicting and cannot be approved until the conflict is resolved
+Scenario 2 - Buffer change flags a retained request conflict
+Given booking A for 10:00-12:00 is Confirmed and request B for 12:30-14:00 is Pending on the same venue and day, both created with zero setup and turnaround buffers When Venue Staff change setup to 30 minutes and turnaround to 45 minutes Then their half-open occupied windows `[start - setup, end + turnaround)` become A `[09:30,12:45)` and B `[12:00,14:45)`, B is flagged `buffer_conflict` without changing its lifecycle status to Conflicting, and a Venue Staff attempt to approve B is blocked with A identified as the conflict; A remains Confirmed, B remains Pending, and both retain occupancy until the conflict is resolved
 Scenario 3 - Simultaneous approval fails safely
 Given another Venue Staff member approves a conflicting request moments before me When my approval is processed Then it fails and I am told the venue has just been taken
-Scenario 4 - Buffered windows are what must not overlap
-Given two pending requests on one venue whose advertised times do not overlap but whose buffered occupancy windows do When both are approved at the same moment Then at most one approval succeeds and the other fails safely, because the database-level conflict check operates on the buffered window (C-65, T-66, ADR-003)
+Scenario 4 - Simultaneous submissions enforce buffered occupancy
+Given a free venue has setup 30 minutes and turnaround 45 minutes and assigned Coordinators prepare requests for 10:00-12:00 and 12:30-14:00 on the same day When both requests are submitted simultaneously Then at most one Pending row is created and the losing submission fails safely with a conflict, because the half-open occupied windows `[start - setup, end + turnaround)` are `[09:30,12:45)` and `[12:00,14:45)` and overlap; the database guard checks buffered occupancy at submission, and no approval is performed (C-65, T-66, ADR-003)
 Scenario 5 - Conflicts are per venue, not per event
 Given one event has Pending requests on two different venues over the same period When both are approved Then both become Confirmed, because double-booking is detected per venue and an event may legitimately occupy several venues at once (C-67, T-68)
 Checklist
 - Be blocked from approving a request overlapping an existing confirmed booking
 - See which existing booking is causing the conflict
-- Confirm a competing pending request is flagged as conflicting once one is approved
+- Confirm a buffer edit flags B with `buffer_conflict`, blocks its approval with A identified, and retains A as Confirmed and B as Pending with both still occupying
+- Confirm simultaneous submissions with overlapping buffered windows create at most one Pending row and return a safe conflict to the loser without approving either
 - Confirm a simultaneous approval by another Venue Staff member fails safely
 - Be told the venue has been taken when a simultaneous approval wins
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -6357,39 +6463,39 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -6405,39 +6511,39 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -6453,39 +6559,39 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -6504,39 +6610,39 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -6549,39 +6655,39 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -6597,39 +6703,39 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -6648,39 +6754,39 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E07-S08</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Link equipment requests and reservations to Sessions</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want equipment requests and reservations to identify the Session they support so that availability and fulfilment use the correct Session period.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request linked to its Session
 Given an Event has multiple Sessions When an Event Coordinator records equipment needed for one Session Then the request is linked to that Session and remains part of the Event
@@ -6697,37 +6803,37 @@
 - Keep technical-support staff assignment event-level</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>C-107, T-74, T-79</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E07-S09</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Preserve reservation warnings when stock reductions overlap withdrawals</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want catalogue stock reductions to account for dated equipment withdrawals so that reservations which no longer fit are flagged and their Coordinators are notified.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reduced usable stock flags reservations
 Given an item has total stock 10, four units withdrawn and five units reserved for the same future period When I reduce total stock to 8 Then the save succeeds, the reservation remains reserved but is marked for review, and its assigned active Coordinator receives one notification and an outbox record
@@ -6743,37 +6849,37 @@
 - Roll back stock, flags and notification/outbox writes together on failure</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>E08-S01</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>View readiness of an event</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see whether venue, equipment and technical support are ready so that I know what still needs my attention.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Arrangement states shown
 Given an event is in planning When I open its readiness view Then each arrangement is shown as complete, in progress or not started
@@ -6781,39 +6887,39 @@
 Given an arrangement is not started When I view it Then the responsible role and the action required are shown</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>E08-S02</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Track outstanding actions across events</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a list of upcoming events with incomplete arrangements so that nothing is overlooked before an event takes place.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete events listed by date
 Given I have upcoming events with incomplete arrangements When I open my outstanding actions list Then those events are listed with the specific incomplete items, ordered by event date
@@ -6821,40 +6927,40 @@
 Given an event is close to its date and arrangements are still incomplete When I view the list Then that event is highlighted as urgent</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>C-28</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.
 Amended in place for the Week 7 Customer Changes (C-70, T-71; this story is To Do, T-74). Completing the arrangements no longer sets Confirmed directly: it lets the Coordinator submit the event for its Operational Safety Check, which moves it to the new Safety Review status, and the Safety Officer's approval (E08-S06) is what sets Confirmed. The readiness checks below are unchanged in substance; what they now gate is the submission. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event submitted for safety review
 Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, its full requested equipment is reserved and any requested technical support is assigned When I submit the event for its Operational Safety Check Then the status becomes Safety Review, the Safety Officer is notified, the Organiser is told the event is awaiting its safety check, and the event becomes Confirmed only when the Safety Officer approves it (E08-S06) (C-67, T-68, C-70, T-71; assumes O-28, O-39, O-40)
@@ -6880,39 +6986,39 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28, C-70, T-71, T-74, O-39, O-40</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a confirmed event to return to Planning when an arrangement requires it so that the system reflects the event's readiness and starts safety review at the right time.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Manual reversion records a reason
 Given an event is Confirmed When I deliberately revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -6933,39 +7039,39 @@
 - Retain earlier safety decisions in history without reusing them</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28, C-70, T-71, C-120, T-81, C-132, T-82</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -6983,40 +7089,40 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>E08-S06</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Conduct the Operational Safety Check as the Safety Officer</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>As a Safety Officer, I want to review the operational safety of each event whose venue and technical arrangements are confirmed, and approve it, reject its safety arrangement or request changes, so that no event proceeds to preparation until it is safe to run.
 New story from the Week 7 Customer Changes (C-70) and the seventh role (T-72). The Safety Review status it works on sits between Planning and Confirmed as an interim placement (T-71); O-39 asks the customer to confirm. The customer guarantees a response, so there is no timeout path. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events awaiting review listed with what the check needs
 Given events are in Safety Review When I open my queue Then each shows the event name, date and time, every confirmed venue with its capacity, layout and known restrictions, expected attendance, accessibility requirements, equipment and its placement, and the time it entered Safety Review, oldest first
@@ -7049,37 +7155,37 @@
 - Confirm every decision is in the activity log</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>C-70, T-71, T-72, T-73, T-74, O-39, O-40, O-41, O-42, O-43</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register once for a confirmed Event and select the Sessions I will attend so that my place is reserved across the Event I chose.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open Event
 Given an Event is Confirmed, registration is open, and selected Sessions have capacity When I submit the required registration information and select one or more Sessions Then one active Event-level registration records those Sessions and I receive a confirmation with the Event and selected Session details
@@ -7100,39 +7206,39 @@
 - See the primary Event venue and the venue for each selected Session</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>C-35, C-67, C-97, C-107, T-68, T-78, T-79, T-85</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want the system to enforce each selected Session's approved layout capacity and the combined Event capacity so that registrations do not exceed either limit.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Both capacity limits enforced
 Given a registration selects one or more Sessions When the request is within each selected Session's approved layout capacity and within the combined Event capacity Then it may be confirmed; if either limit would be exceeded it is not confirmed as an approved seat (C-78, T-85)
@@ -7158,39 +7264,39 @@
 - Allow manual VIP additions only within both limits and block them at either limit</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, C-78, C-98, T-30, T-31, T-50, T-85, B-11, O-50</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set one registration and withdrawal window for the Event so that attendees can select Sessions within a consistent Event-level period.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the Event-level registration opening date has not been reached When an Attendee views the Event Then registration is shown as not yet open and the opening date is stated
@@ -7209,39 +7315,39 @@
 - Warn when the closing date is after the Event has started</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42, T-79, T-85</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given the combined Event capacity is full and its Event-level waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released (Session-specific waiting-list behavior remains open under O-50)
@@ -7260,39 +7366,39 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10, O-50</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my Event registration so that my Event place and places in all selected Sessions are released together.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn from Event and Sessions
 Given I have an active Event registration selecting one or more Sessions and the withdrawal deadline has not passed When I withdraw Then the Event registration is cancelled and its approved places are released from every selected Session and from the combined Event capacity
@@ -7304,39 +7410,39 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10, T-79, T-85</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -7352,39 +7458,39 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -7402,39 +7508,39 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my Event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the Event
@@ -7456,39 +7562,39 @@
 - Confirm Pending requests become Obsolete with history when the Event becomes Completed or Cancelled</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G68" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, C-77, T-16, T-88</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to identify which Session arrangements a change affects so that I re-check the right bookings and reservations.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Session attendance beyond capacity flagged
 Given a Session has a confirmed venue booking When its expected attendance changes Then each booking whose own headcount is set uses that headcount, otherwise it uses the Session attendance; only a booking whose governing headcount exceeds capacity is flagged and Venue Staff are notified
@@ -7511,39 +7617,39 @@
 - Notify staff responsible for the affected arrangements</t>
         </is>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27, C-107, T-79</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr"/>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>E10-S03</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Reschedule an event</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to reschedule an Event while identifying the Session arrangements that must be reconfirmed so that it can still take place when the original dates no longer work.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Session date change flags its arrangements
 Given an Event has confirmed Session venue bookings or equipment reservations When I change one Session's date or time Then only that Session's existing arrangements are flagged for reconfirmation and are not moved silently
@@ -7560,39 +7666,39 @@
 - Close Pending change requests as Obsolete when the Event becomes Completed or Cancelled</t>
         </is>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G70" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>C-25, O-18, C-77, C-107, T-79, T-88</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr"/>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an Event and release its Session arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled and Session arrangements released
 Given an Event Organiser requests cancellation When I cancel the Event and record a reason Then its status becomes Cancelled, all Session venue bookings and equipment reservations are released, calendars/availability are updated, and affected staff are notified
@@ -7613,40 +7719,40 @@
 - Close Pending change requests as Obsolete with history</t>
         </is>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G71" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, C-77, T-07, T-48, T-79, T-88</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr"/>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>E10-S05</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Handle a venue lost from a confirmed event</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
 Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Lost venue flags the event
 Given my event has a Pending or Confirmed venue booking When Venue Staff mark that venue unavailable over the booking's period (E05-S06) Then I am notified, the booking shows as Conflicting on the event, and the event is flagged as needing alternative arrangements while its status and every other arrangement stay as they were (assumes O-24)
@@ -7664,39 +7770,39 @@
 - Confirm the Organiser and registered Attendees are told of the venue change only when it actually happens</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>C-66, C-61, T-28, T-67, T-73, T-74, O-24, O-25</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr"/>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -7724,39 +7830,39 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70, C-70, T-71</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr"/>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>E11-S03</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Receive reminders about upcoming commitments</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want reminders about upcoming events I am supporting so that equipment and support are prepared in time.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reminder lists requirements
 Given I am assigned to an upcoming event When the reminder point before it is reached Then I receive a reminder listing the equipment and support required
@@ -7764,39 +7870,39 @@
 Given an event is cancelled before its reminder is due When the reminder point is reached Then no reminder is sent</t>
         </is>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="G74" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>C-28, O-11</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr"/>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>E11-S04</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Alert on incomplete arrangements</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when an upcoming event still has incomplete arrangements so that I can act while there is still time.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete items named
 Given an upcoming event has an incomplete essential arrangement When the alert point before it is reached Then I receive an alert naming the incomplete items
@@ -7804,39 +7910,39 @@
 Given all arrangements are completed before the alert point When the alert point is reached Then no alert is sent</t>
         </is>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="G75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr"/>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>E12-S01</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>View my events in a calendar</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see my events in a calendar so that I can plan my workload across the coming weeks.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events shown on their dates
 Given I have events spread across several weeks When I open the calendar Then my events appear on their dates with their status indicated
@@ -7844,39 +7950,39 @@
 Given an event spans several days When I view the calendar Then it is shown across all its days rather than only the first</t>
         </is>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="G76" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr"/>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>E12-S02</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Search and filter events</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search events by name, client, date, venue, status, category or assigned Coordinator so that I can find a specific event quickly.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Permitted matches returned
 Given events match my criteria When I search Then only matching events that I am permitted to see are returned
@@ -7886,39 +7992,39 @@
 Given I apply several filters at once When I search Then all the filters are applied together</t>
         </is>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="G77" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr"/>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>E12-S03</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>See my work on a role-based dashboard</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want a dashboard showing booking requests awaiting my decision and upcoming venue preparations so that I can see my outstanding work in one place.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Pending decisions listed
 Given booking requests are pending my decision When I open my dashboard Then they are listed with event name, venue, dates and how long each has been waiting
@@ -7926,39 +8032,39 @@
 Given I have no outstanding items When I open my dashboard Then an empty state is shown rather than an error</t>
         </is>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="G78" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr"/>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>E12-S04</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Use the system on a mobile device</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to use the system on my phone while preparing a venue so that I can check and update arrangements without returning to a desk.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Readable without horizontal scrolling
 Given I open the system on a mobile device When I view my dashboard, an event or a venue calendar Then the content is readable and usable without horizontal scrolling
@@ -7966,39 +8072,39 @@
 Given I am working on a mobile device When I update a preparation status Then the update is saved exactly as it would be on a desktop</t>
         </is>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="G79" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr"/>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>E13-S01</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Generate an event report</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to generate a summary report for an event so that I can share the arrangements at operational meetings.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Generate a downloadable report containing event name, date and time, venue, equipment list, assigned technical support and total registered Attendees
@@ -8007,39 +8113,39 @@
 - Show a clear error with a retry option if generation fails</t>
         </is>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="G80" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr"/>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>E13-S02</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Review venue usage over a period</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to review venue bookings and usage over a chosen period so that I can plan maintenance and identify under-used spaces.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Select a custom date range with start and end dates
@@ -8049,39 +8155,39 @@
 - See an informative empty state when no records match</t>
         </is>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="G81" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr"/>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>E13-S03</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Export attendee registration information</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to export the registration list for my event so that I can prepare badges and catering numbers.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Export registrations only for events the Organiser manages
@@ -8089,39 +8195,39 @@
 - Exclude sensitive personal data from the generated file</t>
         </is>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="G82" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr"/>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>E14-S01</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>View an event's change history</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see how an event's important information has changed over time so that I can explain how the current arrangements were reached.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before and after values listed
 Given an event's date, venue, attendance or status has changed When I open its change history Then each change is listed with the previous value, the new value, who made it and when
@@ -8129,39 +8235,39 @@
 Given I am not permitted to view a particular change When I open the history Then that entry is not shown to me</t>
         </is>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="G83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr"/>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log; access-denial entries are not shown in that log
@@ -8183,39 +8289,39 @@
 - Verify denial and deactivation entries in a controlled test database; no Administrator sign-in is required</t>
         </is>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="G84" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>T-04, T-75, T-76</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr"/>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>E14-S03</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Read edited Activity log dates and times in Singapore time</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser or the assigned Event Coordinator, I want edited date/time values in my existing event Activity log to be readable in Singapore time so that I can understand the recorded edit without interpreting raw UTC strings.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Both existing readers see Singapore time
 Given an authorised Organiser or assigned Coordinator opens the existing event Activity log When an entry displays an edited date/time field value Then each date/time value already displayed by that view uses the existing shared Singapore formatter, including both old and new values where already shown, independently of the browser timezone; 2026-10-15T09:30:00Z represents 15 October 2026 at 17:30 Singapore time, not 16 October. Existing field keys are startAt, endAt and registrationDates; registrationDates stores "opensAt to closesAt", so both endpoints are formatted for display without changing that stored string.
@@ -8235,13 +8341,13 @@
 - Obtain human code/test review and future T-65/T-93 manual evidence; these planned cases are not execution evidence</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>T-93</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>T-97</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 161026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 161026.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1706,28 +1706,82 @@
       <c r="I23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>E03-S11</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Let the Organiser edit registration setup and fix the date layout</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser, I want to fill in and correct the registration setup on my event request, and read the registration dates clearly, so that a request that left the registration setup blank can still be completed for approval.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Organiser edits registration setup before approval
+Given my event has not yet been approved When I edit its registration setup Then the change is saved against the event and recorded in the activity log
+Scenario 2 - Registration setup cannot be cleared
+Given my event has a registration setup When I try to save it empty Then the save is blocked and the recorded registration setup is unchanged
+Scenario 3 - Registration setup restricted for the Organiser after approval
+Given my event has been approved When I open its edit form Then the registration setup is read-only and I am directed to raise a change request (E10-S01)
+Scenario 4 - Coordinator edits registration setup after approval
+Given an event has been approved When I edit its registration setup as the assigned Coordinator Then the change is saved and recorded in the activity log
+Scenario 5 - Registration dates laid out clearly
+Given I am editing an event When I view the Registration section Then "Registration opens" and "Registration closes" are shown as two separate labelled fields, each label with its own input, with no sideways scrolling at phone width
+Checklist
+- Edit the registration setup as the Organiser before approval, with the edit recorded in the activity log
+- Be blocked when saving an empty registration setup
+- See the registration setup read-only after approval, with a link to request a change
+- Edit the registration setup as the assigned Coordinator after approval, with the edit recorded in the activity log
+- See "Registration opens" and "Registration closes" as two labelled fields at desktop and phone width</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>C-52, T-16, T-74</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>E04-S02</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Create a multi-session event</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to define an event made up of one or more Sessions so that each Session's requirements can be planned separately.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Sessions hold their own requirements
 Given I am creating an event When I add one or more Sessions Then each Session stores its date, time, expected attendance, venue requirements, and equipment requirements beneath the Event
@@ -1747,43 +1801,43 @@
 - Delete a Session and release its confirmed booking with notification and history</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>C-19, C-62, C-107, T-48, T-79, T-85</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>E05-S01</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Maintain the venue catalogue</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to add and update venue records so that Event Coordinators search against accurate information.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue added and searchable
 Given I am adding a venue When I save it with location, capacity, facilities, accessibility features, supported layouts and operating hours Then it becomes searchable by Event Coordinators
@@ -1802,47 +1856,47 @@
 - Be blocked from retiring a venue with future bookings, with those bookings identified</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>T-13, T-18, B-05</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>E05-S02</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Match layout requirements to venue capacity</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the room layouts supported by a venue and the maximum capacity for each layout, so that Event Coordinators only consider arrangements the venue can accommodate.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Layout and capacity stored
 Given I am editing a venue When I add a supported layout with its maximum capacity Then it is stored against that venue
@@ -1858,47 +1912,47 @@
 - Be warned when adding a layout that already exists</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>T-45, B-07</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>E05-S03</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>View the venue availability calendar</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to view a venue's calendar so that I can see when the venue is free, pending, confirmed or blocked.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Four states distinguishable
 Given a venue has bookings and blocks in a period When I open its calendar for that period Then each entry is shown as Free, Tentative, Confirmed or Blocked, and the states are visually distinguishable
@@ -1915,43 +1969,43 @@
 - See periods I cannot view marked unavailable without any event detail</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>C-40, C-60, T-17, T-49</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>E05-S04</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Block a venue for maintenance</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to block a venue for maintenance, renovation or safety reasons so that it is not offered for events during that period.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Free period blocked
 Given a venue has no bookings in a period When I block that period and record a reason Then the venue no longer appears as available for those dates
@@ -1967,44 +2021,44 @@
 - Confirm affected Event Coordinators are notified when a block affects an upcoming event</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>E05-S05</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Apply setup and turnaround time</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the setup and turnaround time each venue requires so that every availability and conflict check accounts for the time needed to prepare the room before an event and reset it afterwards.
 Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03, and Scenario 7 here rather than in E06-S01, because both of those stories are Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Buffers recorded on the venue
 Given I am creating or editing a venue When I enter a setup time and a turnaround time in whole minutes, either of which may be 0, and save Then both values are stored against the venue and shown on its detail, and every venue that existed before this story has both values at 0
@@ -2028,44 +2082,44 @@
 - Never have a booking released automatically because a buffer changed</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>C-65, T-66, T-73, T-74, O-20, O-21, O-22 (supersedes C-18, C-38)</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mark a venue temporarily unavailable over existing bookings</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to mark a venue temporarily unavailable for maintenance, equipment failure, renovation, a safety concern or another operational reason, even when events are already booked in it, so that affected bookings are identified and their Coordinators can arrange an alternative without the events themselves being cancelled.
 New story from the Week 7 Customer Changes (C-66). It supersedes E05-S04 Scenario 2, which refused a block over a confirmed booking; E05-S04 is in the Sprint 2 sprint backlog and is not edited (T-67, T-74). Estimate to be set by planning poker at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Unavailability recorded with a reason
 Given I am viewing a venue When I mark it unavailable for a period and choose a reason category from maintenance, equipment failure, renovation, safety concern or other, with a free-text note Then the unavailability is saved with the period, the category, the note and my identity, and the calendar shows the period as Blocked
@@ -2089,41 +2143,41 @@
 - Confirm E05-S04's existing block, shorten and remove behaviour still works for periods with no bookings</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>C-66, C-48, C-61, T-28, T-67, T-74, O-23, O-24, O-25, O-26</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -2142,43 +2196,43 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>B-08</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -2207,43 +2261,43 @@
 - Identify outside operating hours as an advisory failure in E06-S02, without adding that rule to E06-S01</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-48 (supersedes T-21), T-77, B-08</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -2304,43 +2358,43 @@
 - Complete TC_E06S03_09 to _13 under the current Sprint 3 plan; record anything unfinished honestly at sprint close (PO confirmation, 16 October; T-94)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, T-78, O-27, O-29, O-30, T-94, T-95, T-96</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -2364,48 +2418,48 @@
 - Verify all three booking-log outcomes under TC_E06S04_05, TC_E06S04_06 and TC_E06S04_07</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66, T-75, T-76</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
 The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
@@ -2438,43 +2492,43 @@
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, T-78, T-92, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
@@ -2495,43 +2549,43 @@
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -2548,43 +2602,43 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -2600,43 +2654,43 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -2652,43 +2706,43 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -2707,43 +2761,43 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -2756,43 +2810,43 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -2808,43 +2862,43 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -2863,39 +2917,39 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E07-S08</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Link equipment requests and reservations to Sessions</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want equipment requests and reservations to identify the Session they support so that availability and fulfilment use the correct Session period.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request linked to its Session
 Given an Event has multiple Sessions When an Event Coordinator records equipment needed for one Session Then the request is linked to that Session and remains part of the Event
@@ -2912,37 +2966,37 @@
 - Keep technical-support staff assignment event-level</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>C-107, T-74, T-79</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E07-S09</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Preserve reservation warnings when stock reductions overlap withdrawals</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want catalogue stock reductions to account for dated equipment withdrawals so that reservations which no longer fit are flagged and their Coordinators are notified.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reduced usable stock flags reservations
 Given an item has total stock 10, four units withdrawn and five units reserved for the same future period When I reduce total stock to 8 Then the save succeeds, the reservation remains reserved but is marked for review, and its assigned active Coordinator receives one notification and an outbox record
@@ -2958,42 +3012,42 @@
 - Roll back stock, flags and notification/outbox writes together on failure</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.
 Amended in place for the Week 7 Customer Changes (C-70, T-71; this story is To Do, T-74). Completing the arrangements no longer sets Confirmed directly: it lets the Coordinator submit the event for its Operational Safety Check, which moves it to the new Safety Review status, and the Safety Officer's approval (E08-S06) is what sets Confirmed. The readiness checks below are unchanged in substance; what they now gate is the submission. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event submitted for safety review
 Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, its full requested equipment is reserved and any requested technical support is assigned When I submit the event for its Operational Safety Check Then the status becomes Safety Review, the Safety Officer is notified, the Organiser is told the event is awaiting its safety check, and the event becomes Confirmed only when the Safety Officer approves it (E08-S06) (C-67, T-68, C-70, T-71; assumes O-28, O-39, O-40)
@@ -3019,43 +3073,43 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28, C-70, T-71, T-74, O-39, O-40</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a confirmed event to return to Planning when an arrangement requires it so that the system reflects the event's readiness and starts safety review at the right time.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Manual reversion records a reason
 Given an event is Confirmed When I deliberately revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -3076,43 +3130,43 @@
 - Retain earlier safety decisions in history without reusing them</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28, C-70, T-71, C-120, T-81, C-132, T-82</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -3130,44 +3184,44 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E08-S06</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Conduct the Operational Safety Check as the Safety Officer</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As a Safety Officer, I want to review the operational safety of each event whose venue and technical arrangements are confirmed, and approve it, reject its safety arrangement or request changes, so that no event proceeds to preparation until it is safe to run.
 New story from the Week 7 Customer Changes (C-70) and the seventh role (T-72). The Safety Review status it works on sits between Planning and Confirmed as an interim placement (T-71); O-39 asks the customer to confirm. The customer guarantees a response, so there is no timeout path. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events awaiting review listed with what the check needs
 Given events are in Safety Review When I open my queue Then each shows the event name, date and time, every confirmed venue with its capacity, layout and known restrictions, expected attendance, accessibility requirements, equipment and its placement, and the time it entered Safety Review, oldest first
@@ -3200,41 +3254,41 @@
 - Confirm every decision is in the activity log</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>C-70, T-71, T-72, T-73, T-74, O-39, O-40, O-41, O-42, O-43</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register once for a confirmed Event and select the Sessions I will attend so that my place is reserved across the Event I chose.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open Event
 Given an Event is Confirmed, registration is open, and selected Sessions have capacity When I submit the required registration information and select one or more Sessions Then one active Event-level registration records those Sessions and I receive a confirmation with the Event and selected Session details
@@ -3255,43 +3309,43 @@
 - See the primary Event venue and the venue for each selected Session</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-35, C-67, C-97, C-107, T-68, T-78, T-79, T-85</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want the system to enforce each selected Session's approved layout capacity and the combined Event capacity so that registrations do not exceed either limit.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Both capacity limits enforced
 Given a registration selects one or more Sessions When the request is within each selected Session's approved layout capacity and within the combined Event capacity Then it may be confirmed; if either limit would be exceeded it is not confirmed as an approved seat (C-78, T-85)
@@ -3317,43 +3371,43 @@
 - Allow manual VIP additions only within both limits and block them at either limit</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, C-78, C-98, T-30, T-31, T-50, T-85, B-11, O-50</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set one registration and withdrawal window for the Event so that attendees can select Sessions within a consistent Event-level period.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the Event-level registration opening date has not been reached When an Attendee views the Event Then registration is shown as not yet open and the opening date is stated
@@ -3372,43 +3426,43 @@
 - Warn when the closing date is after the Event has started</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42, T-79, T-85</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given the combined Event capacity is full and its Event-level waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released (Session-specific waiting-list behavior remains open under O-50)
@@ -3427,43 +3481,43 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10, O-50</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my Event registration so that my Event place and places in all selected Sessions are released together.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn from Event and Sessions
 Given I have an active Event registration selecting one or more Sessions and the withdrawal deadline has not passed When I withdraw Then the Event registration is cancelled and its approved places are released from every selected Session and from the combined Event capacity
@@ -3475,43 +3529,43 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10, T-79, T-85</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -3527,43 +3581,43 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -3581,43 +3635,43 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my Event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the Event
@@ -3639,43 +3693,43 @@
 - Confirm Pending requests become Obsolete with history when the Event becomes Completed or Cancelled</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, C-77, T-16, T-88</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to identify which Session arrangements a change affects so that I re-check the right bookings and reservations.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Session attendance beyond capacity flagged
 Given a Session has a confirmed venue booking When its expected attendance changes Then each booking whose own headcount is set uses that headcount, otherwise it uses the Session attendance; only a booking whose governing headcount exceeds capacity is flagged and Venue Staff are notified
@@ -3698,43 +3752,43 @@
 - Notify staff responsible for the affected arrangements</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27, C-107, T-79</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an Event and release its Session arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled and Session arrangements released
 Given an Event Organiser requests cancellation When I cancel the Event and record a reason Then its status becomes Cancelled, all Session venue bookings and equipment reservations are released, calendars/availability are updated, and affected staff are notified
@@ -3755,44 +3809,44 @@
 - Close Pending change requests as Obsolete with history</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, C-77, T-07, T-48, T-79, T-88</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>E10-S05</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Handle a venue lost from a confirmed event</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
 Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Lost venue flags the event
 Given my event has a Pending or Confirmed venue booking When Venue Staff mark that venue unavailable over the booking's period (E05-S06) Then I am notified, the booking shows as Conflicting on the event, and the event is flagged as needing alternative arrangements while its status and every other arrangement stay as they were (assumes O-24)
@@ -3810,43 +3864,43 @@
 - Confirm the Organiser and registered Attendees are told of the venue change only when it actually happens</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>C-66, C-61, T-28, T-67, T-73, T-74, O-24, O-25</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -3874,43 +3928,43 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70, C-70, T-71</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log; access-denial entries are not shown in that log
@@ -3932,15 +3986,15 @@
 - Verify denial and deactivation entries in a controlled test database; no Administrator sign-in is required</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>T-04, T-75, T-76</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
@@ -3957,7 +4011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5380,25 +5434,75 @@
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>E03-S11</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Let the Organiser edit registration setup and fix the date layout</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser, I want to fill in and correct the registration setup on my event request, and read the registration dates clearly, so that a request that left the registration setup blank can still be completed for approval.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Organiser edits registration setup before approval
+Given my event has not yet been approved When I edit its registration setup Then the change is saved against the event and recorded in the activity log
+Scenario 2 - Registration setup cannot be cleared
+Given my event has a registration setup When I try to save it empty Then the save is blocked and the recorded registration setup is unchanged
+Scenario 3 - Registration setup restricted for the Organiser after approval
+Given my event has been approved When I open its edit form Then the registration setup is read-only and I am directed to raise a change request (E10-S01)
+Scenario 4 - Coordinator edits registration setup after approval
+Given an event has been approved When I edit its registration setup as the assigned Coordinator Then the change is saved and recorded in the activity log
+Scenario 5 - Registration dates laid out clearly
+Given I am editing an event When I view the Registration section Then "Registration opens" and "Registration closes" are shown as two separate labelled fields, each label with its own input, with no sideways scrolling at phone width
+Checklist
+- Edit the registration setup as the Organiser before approval, with the edit recorded in the activity log
+- Be blocked when saving an empty registration setup
+- See the registration setup read-only after approval, with a link to request a change
+- Edit the registration setup as the assigned Coordinator after approval, with the edit recorded in the activity log
+- See "Registration opens" and "Registration closes" as two labelled fields at desktop and phone width</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>C-52, T-16, T-74</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>E04-S01</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Record the event programme</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to record the programme for my event, including sessions and breaks, so that ConnectSphere can plan the venue and support around it.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Programme item added
 Given I am editing my event When I add a programme item with a title, start time and end time Then it appears in the event in chronological order
@@ -5408,39 +5512,39 @@
 Given two programme items overlap When I save them Then I am warned of the overlap</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>T-19</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>E04-S02</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Create a multi-session event</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to define an event made up of one or more Sessions so that each Session's requirements can be planned separately.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Sessions hold their own requirements
 Given I am creating an event When I add one or more Sessions Then each Session stores its date, time, expected attendance, venue requirements, and equipment requirements beneath the Event
@@ -5460,39 +5564,39 @@
 - Delete a Session and release its confirmed booking with notification and history</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>C-19, C-62, C-107, T-48, T-79, T-85</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>E05-S01</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Maintain the venue catalogue</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to add and update venue records so that Event Coordinators search against accurate information.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue added and searchable
 Given I am adding a venue When I save it with location, capacity, facilities, accessibility features, supported layouts and operating hours Then it becomes searchable by Event Coordinators
@@ -5511,39 +5615,39 @@
 - Be blocked from retiring a venue with future bookings, with those bookings identified</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>T-13, T-18, B-05</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>E05-S02</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Match layout requirements to venue capacity</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the room layouts supported by a venue and the maximum capacity for each layout, so that Event Coordinators only consider arrangements the venue can accommodate.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Layout and capacity stored
 Given I am editing a venue When I add a supported layout with its maximum capacity Then it is stored against that venue
@@ -5559,39 +5663,39 @@
 - Be warned when adding a layout that already exists</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>T-45, B-07</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E05-S03</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>View the venue availability calendar</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to view a venue's calendar so that I can see when the venue is free, pending, confirmed or blocked.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Four states distinguishable
 Given a venue has bookings and blocks in a period When I open its calendar for that period Then each entry is shown as Free, Tentative, Confirmed or Blocked, and the states are visually distinguishable
@@ -5608,39 +5712,39 @@
 - See periods I cannot view marked unavailable without any event detail</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>C-40, C-60, T-17, T-49</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>E05-S04</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Block a venue for maintenance</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to block a venue for maintenance, renovation or safety reasons so that it is not offered for events during that period.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Free period blocked
 Given a venue has no bookings in a period When I block that period and record a reason Then the venue no longer appears as available for those dates
@@ -5656,40 +5760,40 @@
 - Confirm affected Event Coordinators are notified when a block affects an upcoming event</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E05-S05</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Apply setup and turnaround time</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the setup and turnaround time each venue requires so that every availability and conflict check accounts for the time needed to prepare the room before an event and reset it afterwards.
 Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03, and Scenario 7 here rather than in E06-S01, because both of those stories are Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Buffers recorded on the venue
 Given I am creating or editing a venue When I enter a setup time and a turnaround time in whole minutes, either of which may be 0, and save Then both values are stored against the venue and shown on its detail, and every venue that existed before this story has both values at 0
@@ -5713,40 +5817,40 @@
 - Never have a booking released automatically because a buffer changed</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>C-65, T-66, T-73, T-74, O-20, O-21, O-22 (supersedes C-18, C-38)</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Mark a venue temporarily unavailable over existing bookings</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to mark a venue temporarily unavailable for maintenance, equipment failure, renovation, a safety concern or another operational reason, even when events are already booked in it, so that affected bookings are identified and their Coordinators can arrange an alternative without the events themselves being cancelled.
 New story from the Week 7 Customer Changes (C-66). It supersedes E05-S04 Scenario 2, which refused a block over a confirmed booking; E05-S04 is in the Sprint 2 sprint backlog and is not edited (T-67, T-74). Estimate to be set by planning poker at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Unavailability recorded with a reason
 Given I am viewing a venue When I mark it unavailable for a period and choose a reason category from maintenance, equipment failure, renovation, safety concern or other, with a free-text note Then the unavailability is saved with the period, the category, the note and my identity, and the calendar shows the period as Blocked
@@ -5770,37 +5874,37 @@
 - Confirm E05-S04's existing block, shorten and remove behaviour still works for periods with no bookings</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>C-66, C-48, C-61, T-28, T-67, T-74, O-23, O-24, O-25, O-26</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -5819,39 +5923,39 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>B-08</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -5880,39 +5984,39 @@
 - Identify outside operating hours as an advisory failure in E06-S02, without adding that rule to E06-S01</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-48 (supersedes T-21), T-77, B-08</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -5973,39 +6077,39 @@
 - Complete TC_E06S03_09 to _13 under the current Sprint 3 plan; record anything unfinished honestly at sprint close (PO confirmation, 16 October; T-94)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, T-78, O-27, O-29, O-30, T-94, T-95, T-96</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -6029,40 +6133,40 @@
 - Verify all three booking-log outcomes under TC_E06S04_05, TC_E06S04_06 and TC_E06S04_07</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66, T-75, T-76</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
 The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
@@ -6095,39 +6199,39 @@
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, T-78, T-92, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
@@ -6148,39 +6252,39 @@
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -6197,39 +6301,39 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -6245,39 +6349,39 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -6293,39 +6397,39 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -6344,39 +6448,39 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -6389,39 +6493,39 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -6437,39 +6541,39 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -6488,39 +6592,39 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E07-S08</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Link equipment requests and reservations to Sessions</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want equipment requests and reservations to identify the Session they support so that availability and fulfilment use the correct Session period.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request linked to its Session
 Given an Event has multiple Sessions When an Event Coordinator records equipment needed for one Session Then the request is linked to that Session and remains part of the Event
@@ -6537,37 +6641,37 @@
 - Keep technical-support staff assignment event-level</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-107, T-74, T-79</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E07-S09</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Preserve reservation warnings when stock reductions overlap withdrawals</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want catalogue stock reductions to account for dated equipment withdrawals so that reservations which no longer fit are flagged and their Coordinators are notified.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reduced usable stock flags reservations
 Given an item has total stock 10, four units withdrawn and five units reserved for the same future period When I reduce total stock to 8 Then the save succeeds, the reservation remains reserved but is marked for review, and its assigned active Coordinator receives one notification and an outbox record
@@ -6583,37 +6687,37 @@
 - Roll back stock, flags and notification/outbox writes together on failure</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E08-S01</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>View readiness of an event</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see whether venue, equipment and technical support are ready so that I know what still needs my attention.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Arrangement states shown
 Given an event is in planning When I open its readiness view Then each arrangement is shown as complete, in progress or not started
@@ -6621,39 +6725,39 @@
 Given an arrangement is not started When I view it Then the responsible role and the action required are shown</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>E08-S02</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Track outstanding actions across events</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a list of upcoming events with incomplete arrangements so that nothing is overlooked before an event takes place.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete events listed by date
 Given I have upcoming events with incomplete arrangements When I open my outstanding actions list Then those events are listed with the specific incomplete items, ordered by event date
@@ -6661,40 +6765,40 @@
 Given an event is close to its date and arrangements are still incomplete When I view the list Then that event is highlighted as urgent</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>C-28</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.
 Amended in place for the Week 7 Customer Changes (C-70, T-71; this story is To Do, T-74). Completing the arrangements no longer sets Confirmed directly: it lets the Coordinator submit the event for its Operational Safety Check, which moves it to the new Safety Review status, and the Safety Officer's approval (E08-S06) is what sets Confirmed. The readiness checks below are unchanged in substance; what they now gate is the submission. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event submitted for safety review
 Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, its full requested equipment is reserved and any requested technical support is assigned When I submit the event for its Operational Safety Check Then the status becomes Safety Review, the Safety Officer is notified, the Organiser is told the event is awaiting its safety check, and the event becomes Confirmed only when the Safety Officer approves it (E08-S06) (C-67, T-68, C-70, T-71; assumes O-28, O-39, O-40)
@@ -6720,39 +6824,39 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28, C-70, T-71, T-74, O-39, O-40</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a confirmed event to return to Planning when an arrangement requires it so that the system reflects the event's readiness and starts safety review at the right time.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Manual reversion records a reason
 Given an event is Confirmed When I deliberately revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -6773,39 +6877,39 @@
 - Retain earlier safety decisions in history without reusing them</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28, C-70, T-71, C-120, T-81, C-132, T-82</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -6823,40 +6927,40 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>E08-S06</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Conduct the Operational Safety Check as the Safety Officer</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>As a Safety Officer, I want to review the operational safety of each event whose venue and technical arrangements are confirmed, and approve it, reject its safety arrangement or request changes, so that no event proceeds to preparation until it is safe to run.
 New story from the Week 7 Customer Changes (C-70) and the seventh role (T-72). The Safety Review status it works on sits between Planning and Confirmed as an interim placement (T-71); O-39 asks the customer to confirm. The customer guarantees a response, so there is no timeout path. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events awaiting review listed with what the check needs
 Given events are in Safety Review When I open my queue Then each shows the event name, date and time, every confirmed venue with its capacity, layout and known restrictions, expected attendance, accessibility requirements, equipment and its placement, and the time it entered Safety Review, oldest first
@@ -6889,37 +6993,37 @@
 - Confirm every decision is in the activity log</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>C-70, T-71, T-72, T-73, T-74, O-39, O-40, O-41, O-42, O-43</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register once for a confirmed Event and select the Sessions I will attend so that my place is reserved across the Event I chose.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open Event
 Given an Event is Confirmed, registration is open, and selected Sessions have capacity When I submit the required registration information and select one or more Sessions Then one active Event-level registration records those Sessions and I receive a confirmation with the Event and selected Session details
@@ -6940,39 +7044,39 @@
 - See the primary Event venue and the venue for each selected Session</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>C-35, C-67, C-97, C-107, T-68, T-78, T-79, T-85</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want the system to enforce each selected Session's approved layout capacity and the combined Event capacity so that registrations do not exceed either limit.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Both capacity limits enforced
 Given a registration selects one or more Sessions When the request is within each selected Session's approved layout capacity and within the combined Event capacity Then it may be confirmed; if either limit would be exceeded it is not confirmed as an approved seat (C-78, T-85)
@@ -6998,39 +7102,39 @@
 - Allow manual VIP additions only within both limits and block them at either limit</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, C-78, C-98, T-30, T-31, T-50, T-85, B-11, O-50</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set one registration and withdrawal window for the Event so that attendees can select Sessions within a consistent Event-level period.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the Event-level registration opening date has not been reached When an Attendee views the Event Then registration is shown as not yet open and the opening date is stated
@@ -7049,39 +7153,39 @@
 - Warn when the closing date is after the Event has started</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42, T-79, T-85</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given the combined Event capacity is full and its Event-level waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released (Session-specific waiting-list behavior remains open under O-50)
@@ -7100,39 +7204,39 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10, O-50</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my Event registration so that my Event place and places in all selected Sessions are released together.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn from Event and Sessions
 Given I have an active Event registration selecting one or more Sessions and the withdrawal deadline has not passed When I withdraw Then the Event registration is cancelled and its approved places are released from every selected Session and from the combined Event capacity
@@ -7144,39 +7248,39 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10, T-79, T-85</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -7192,39 +7296,39 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -7242,39 +7346,39 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my Event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the Event
@@ -7296,39 +7400,39 @@
 - Confirm Pending requests become Obsolete with history when the Event becomes Completed or Cancelled</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G67" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, C-77, T-16, T-88</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to identify which Session arrangements a change affects so that I re-check the right bookings and reservations.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Session attendance beyond capacity flagged
 Given a Session has a confirmed venue booking When its expected attendance changes Then each booking whose own headcount is set uses that headcount, otherwise it uses the Session attendance; only a booking whose governing headcount exceeds capacity is flagged and Venue Staff are notified
@@ -7351,39 +7455,39 @@
 - Notify staff responsible for the affected arrangements</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G68" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27, C-107, T-79</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>E10-S03</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Reschedule an event</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to reschedule an Event while identifying the Session arrangements that must be reconfirmed so that it can still take place when the original dates no longer work.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Session date change flags its arrangements
 Given an Event has confirmed Session venue bookings or equipment reservations When I change one Session's date or time Then only that Session's existing arrangements are flagged for reconfirmation and are not moved silently
@@ -7400,39 +7504,39 @@
 - Close Pending change requests as Obsolete when the Event becomes Completed or Cancelled</t>
         </is>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>C-25, O-18, C-77, C-107, T-79, T-88</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr"/>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an Event and release its Session arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled and Session arrangements released
 Given an Event Organiser requests cancellation When I cancel the Event and record a reason Then its status becomes Cancelled, all Session venue bookings and equipment reservations are released, calendars/availability are updated, and affected staff are notified
@@ -7453,40 +7557,40 @@
 - Close Pending change requests as Obsolete with history</t>
         </is>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G70" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, C-77, T-07, T-48, T-79, T-88</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr"/>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>E10-S05</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Handle a venue lost from a confirmed event</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
 Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Lost venue flags the event
 Given my event has a Pending or Confirmed venue booking When Venue Staff mark that venue unavailable over the booking's period (E05-S06) Then I am notified, the booking shows as Conflicting on the event, and the event is flagged as needing alternative arrangements while its status and every other arrangement stay as they were (assumes O-24)
@@ -7504,39 +7608,39 @@
 - Confirm the Organiser and registered Attendees are told of the venue change only when it actually happens</t>
         </is>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G71" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>C-66, C-61, T-28, T-67, T-73, T-74, O-24, O-25</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr"/>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -7564,39 +7668,39 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70, C-70, T-71</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr"/>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>E11-S03</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Receive reminders about upcoming commitments</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want reminders about upcoming events I am supporting so that equipment and support are prepared in time.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reminder lists requirements
 Given I am assigned to an upcoming event When the reminder point before it is reached Then I receive a reminder listing the equipment and support required
@@ -7604,39 +7708,39 @@
 Given an event is cancelled before its reminder is due When the reminder point is reached Then no reminder is sent</t>
         </is>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>C-28, O-11</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr"/>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>E11-S04</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Alert on incomplete arrangements</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when an upcoming event still has incomplete arrangements so that I can act while there is still time.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete items named
 Given an upcoming event has an incomplete essential arrangement When the alert point before it is reached Then I receive an alert naming the incomplete items
@@ -7644,39 +7748,39 @@
 Given all arrangements are completed before the alert point When the alert point is reached Then no alert is sent</t>
         </is>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="G74" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr"/>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>E12-S01</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>View my events in a calendar</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see my events in a calendar so that I can plan my workload across the coming weeks.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events shown on their dates
 Given I have events spread across several weeks When I open the calendar Then my events appear on their dates with their status indicated
@@ -7684,39 +7788,39 @@
 Given an event spans several days When I view the calendar Then it is shown across all its days rather than only the first</t>
         </is>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="G75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr"/>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>E12-S02</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Search and filter events</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search events by name, client, date, venue, status, category or assigned Coordinator so that I can find a specific event quickly.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Permitted matches returned
 Given events match my criteria When I search Then only matching events that I am permitted to see are returned
@@ -7726,39 +7830,39 @@
 Given I apply several filters at once When I search Then all the filters are applied together</t>
         </is>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="G76" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr"/>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>E12-S03</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>See my work on a role-based dashboard</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want a dashboard showing booking requests awaiting my decision and upcoming venue preparations so that I can see my outstanding work in one place.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Pending decisions listed
 Given booking requests are pending my decision When I open my dashboard Then they are listed with event name, venue, dates and how long each has been waiting
@@ -7766,39 +7870,39 @@
 Given I have no outstanding items When I open my dashboard Then an empty state is shown rather than an error</t>
         </is>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="G77" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr"/>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>E12-S04</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Use the system on a mobile device</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to use the system on my phone while preparing a venue so that I can check and update arrangements without returning to a desk.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Readable without horizontal scrolling
 Given I open the system on a mobile device When I view my dashboard, an event or a venue calendar Then the content is readable and usable without horizontal scrolling
@@ -7806,39 +7910,39 @@
 Given I am working on a mobile device When I update a preparation status Then the update is saved exactly as it would be on a desktop</t>
         </is>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="G78" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr"/>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>E13-S01</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Generate an event report</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to generate a summary report for an event so that I can share the arrangements at operational meetings.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Generate a downloadable report containing event name, date and time, venue, equipment list, assigned technical support and total registered Attendees
@@ -7847,39 +7951,39 @@
 - Show a clear error with a retry option if generation fails</t>
         </is>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="G79" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr"/>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>E13-S02</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Review venue usage over a period</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to review venue bookings and usage over a chosen period so that I can plan maintenance and identify under-used spaces.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Select a custom date range with start and end dates
@@ -7889,39 +7993,39 @@
 - See an informative empty state when no records match</t>
         </is>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="G80" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr"/>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>E13-S03</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Export attendee registration information</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to export the registration list for my event so that I can prepare badges and catering numbers.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Export registrations only for events the Organiser manages
@@ -7929,39 +8033,39 @@
 - Exclude sensitive personal data from the generated file</t>
         </is>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="G81" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr"/>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>E14-S01</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>View an event's change history</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see how an event's important information has changed over time so that I can explain how the current arrangements were reached.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before and after values listed
 Given an event's date, venue, attendance or status has changed When I open its change history Then each change is listed with the previous value, the new value, who made it and when
@@ -7969,39 +8073,39 @@
 Given I am not permitted to view a particular change When I open the history Then that entry is not shown to me</t>
         </is>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="G82" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr"/>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log; access-denial entries are not shown in that log
@@ -8023,15 +8127,15 @@
 - Verify denial and deactivation entries in a controlled test database; no Administrator sign-in is required</t>
         </is>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="G83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>T-04, T-75, T-76</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/CONNECTSPHERE BACKLOGS CAA 161026.xlsx
+++ b/docs/CONNECTSPHERE BACKLOGS CAA 161026.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1760,28 +1760,83 @@
       <c r="I24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>E03-S12</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Show consistent Organiser save success status</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser, I want confirmation of a saved event edit to use the shared success Alert so that I can recognise the same clear save outcome used on the Coordinator's event page.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Shared success Alert after a saved edit
+Given I may edit an event When a changed field saves successfully Then the event detail shows the existing field-specific saved message through the shared Alert with tone="success", retaining role="status" rather than replacing it with an urgent alert or plain paragraph.
+Scenario 2 - Saved data and audit survive reload
+Given an allowed event edit succeeds When the record reloads and I reopen it Then the changed value is retained and its existing activity-log entry remains available, with no extra save or audit write caused by rendering the confirmation.
+Scenario 3 - Failure cannot report success
+Given a new edit is invalid or its save request fails When I attempt to save Then the existing validation or error feedback remains and no success Alert claims that attempt was saved; starting a new edit clears the previous save confirmation.
+Scenario 4 - Cancellation and permissions unchanged
+Given I cancel an edit or attempt a field I cannot edit under the current event status and access rules When the attempt ends Then cancellation produces no save confirmation or mutation, and existing restrictions and change-request routing remain in force.
+Checklist
+- Reuse frontend/src/shared/feedback.tsx Alert in frontend/src/features/organiser/ClientEvents.tsx; preserve field-specific text and polite status semantics
+- Cover successful save/reload/audit, invalid input, failed request after a prior success, cancellation and restricted fields with TC_E03S12_01 to _05
+- Leave the Coordinator save flow, all other Organiser workflows, permissions and notifications unchanged; no redesign or new notification
+- Obtain human review of code and test cases and future manual evidence before claiming delivery; this definition does not execute those cases</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>T-93</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Le Xin</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>E04-S02</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Create a multi-session event</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to define an event made up of one or more Sessions so that each Session's requirements can be planned separately.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Sessions hold their own requirements
 Given I am creating an event When I add one or more Sessions Then each Session stores its date, time, expected attendance, venue requirements, and equipment requirements beneath the Event
@@ -1801,43 +1856,43 @@
 - Delete a Session and release its confirmed booking with notification and history</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>C-19, C-62, C-107, T-48, T-79, T-85</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>E05-S01</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Maintain the venue catalogue</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to add and update venue records so that Event Coordinators search against accurate information.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue added and searchable
 Given I am adding a venue When I save it with location, capacity, facilities, accessibility features, supported layouts and operating hours Then it becomes searchable by Event Coordinators
@@ -1856,47 +1911,47 @@
 - Be blocked from retiring a venue with future bookings, with those bookings identified</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>T-13, T-18, B-05</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>E05-S02</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Match layout requirements to venue capacity</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the room layouts supported by a venue and the maximum capacity for each layout, so that Event Coordinators only consider arrangements the venue can accommodate.</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Layout and capacity stored
 Given I am editing a venue When I add a supported layout with its maximum capacity Then it is stored against that venue
@@ -1912,47 +1967,47 @@
 - Be warned when adding a layout that already exists</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>T-45, B-07</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>E05-S03</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>View the venue availability calendar</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to view a venue's calendar so that I can see when the venue is free, pending, confirmed or blocked.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Four states distinguishable
 Given a venue has bookings and blocks in a period When I open its calendar for that period Then each entry is shown as Free, Tentative, Confirmed or Blocked, and the states are visually distinguishable
@@ -1969,43 +2024,43 @@
 - See periods I cannot view marked unavailable without any event detail</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>C-40, C-60, T-17, T-49</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>E05-S04</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Block a venue for maintenance</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to block a venue for maintenance, renovation or safety reasons so that it is not offered for events during that period.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Free period blocked
 Given a venue has no bookings in a period When I block that period and record a reason Then the venue no longer appears as available for those dates
@@ -2021,44 +2076,44 @@
 - Confirm affected Event Coordinators are notified when a block affects an upcoming event</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>E05-S05</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Apply setup and turnaround time</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the setup and turnaround time each venue requires so that every availability and conflict check accounts for the time needed to prepare the room before an event and reset it afterwards.
 Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03, and Scenario 7 here rather than in E06-S01, because both of those stories are Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Buffers recorded on the venue
 Given I am creating or editing a venue When I enter a setup time and a turnaround time in whole minutes, either of which may be 0, and save Then both values are stored against the venue and shown on its detail, and every venue that existed before this story has both values at 0
@@ -2082,44 +2137,44 @@
 - Never have a booking released automatically because a buffer changed</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>C-65, T-66, T-73, T-74, O-20, O-21, O-22 (supersedes C-18, C-38)</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mark a venue temporarily unavailable over existing bookings</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to mark a venue temporarily unavailable for maintenance, equipment failure, renovation, a safety concern or another operational reason, even when events are already booked in it, so that affected bookings are identified and their Coordinators can arrange an alternative without the events themselves being cancelled.
 New story from the Week 7 Customer Changes (C-66). It supersedes E05-S04 Scenario 2, which refused a block over a confirmed booking; E05-S04 is in the Sprint 2 sprint backlog and is not edited (T-67, T-74). Estimate to be set by planning poker at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Unavailability recorded with a reason
 Given I am viewing a venue When I mark it unavailable for a period and choose a reason category from maintenance, equipment failure, renovation, safety concern or other, with a free-text note Then the unavailability is saved with the period, the category, the note and my identity, and the calendar shows the period as Blocked
@@ -2143,41 +2198,41 @@
 - Confirm E05-S04's existing block, shorten and remove behaviour still works for periods with no bookings</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>C-66, C-48, C-61, T-28, T-67, T-74, O-23, O-24, O-25, O-26</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -2196,43 +2251,43 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>B-08</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -2261,43 +2316,43 @@
 - Identify outside operating hours as an advisory failure in E06-S02, without adding that rule to E06-S01</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-48 (supersedes T-21), T-77, B-08</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -2358,43 +2413,43 @@
 - Complete TC_E06S03_09 to _13 under the current Sprint 3 plan; record anything unfinished honestly at sprint close (PO confirmation, 16 October; T-94)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, T-78, O-27, O-29, O-30, T-94, T-95, T-96</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -2418,48 +2473,48 @@
 - Verify all three booking-log outcomes under TC_E06S04_05, TC_E06S04_06 and TC_E06S04_07</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66, T-75, T-76</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
 The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
@@ -2492,43 +2547,43 @@
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, T-78, T-92, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
@@ -2549,43 +2604,43 @@
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -2602,43 +2657,43 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -2654,43 +2709,43 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -2706,43 +2761,43 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -2761,43 +2816,43 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -2810,43 +2865,43 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -2862,43 +2917,43 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -2917,39 +2972,39 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E07-S08</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Link equipment requests and reservations to Sessions</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want equipment requests and reservations to identify the Session they support so that availability and fulfilment use the correct Session period.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request linked to its Session
 Given an Event has multiple Sessions When an Event Coordinator records equipment needed for one Session Then the request is linked to that Session and remains part of the Event
@@ -2966,37 +3021,37 @@
 - Keep technical-support staff assignment event-level</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>C-107, T-74, T-79</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E07-S09</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Preserve reservation warnings when stock reductions overlap withdrawals</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want catalogue stock reductions to account for dated equipment withdrawals so that reservations which no longer fit are flagged and their Coordinators are notified.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reduced usable stock flags reservations
 Given an item has total stock 10, four units withdrawn and five units reserved for the same future period When I reduce total stock to 8 Then the save succeeds, the reservation remains reserved but is marked for review, and its assigned active Coordinator receives one notification and an outbox record
@@ -3012,42 +3067,42 @@
 - Roll back stock, flags and notification/outbox writes together on failure</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.
 Amended in place for the Week 7 Customer Changes (C-70, T-71; this story is To Do, T-74). Completing the arrangements no longer sets Confirmed directly: it lets the Coordinator submit the event for its Operational Safety Check, which moves it to the new Safety Review status, and the Safety Officer's approval (E08-S06) is what sets Confirmed. The readiness checks below are unchanged in substance; what they now gate is the submission. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event submitted for safety review
 Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, its full requested equipment is reserved and any requested technical support is assigned When I submit the event for its Operational Safety Check Then the status becomes Safety Review, the Safety Officer is notified, the Organiser is told the event is awaiting its safety check, and the event becomes Confirmed only when the Safety Officer approves it (E08-S06) (C-67, T-68, C-70, T-71; assumes O-28, O-39, O-40)
@@ -3073,43 +3128,43 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28, C-70, T-71, T-74, O-39, O-40</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a confirmed event to return to Planning when an arrangement requires it so that the system reflects the event's readiness and starts safety review at the right time.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Manual reversion records a reason
 Given an event is Confirmed When I deliberately revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -3130,43 +3185,43 @@
 - Retain earlier safety decisions in history without reusing them</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28, C-70, T-71, C-120, T-81, C-132, T-82</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -3184,44 +3239,44 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E08-S06</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Conduct the Operational Safety Check as the Safety Officer</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As a Safety Officer, I want to review the operational safety of each event whose venue and technical arrangements are confirmed, and approve it, reject its safety arrangement or request changes, so that no event proceeds to preparation until it is safe to run.
 New story from the Week 7 Customer Changes (C-70) and the seventh role (T-72). The Safety Review status it works on sits between Planning and Confirmed as an interim placement (T-71); O-39 asks the customer to confirm. The customer guarantees a response, so there is no timeout path. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events awaiting review listed with what the check needs
 Given events are in Safety Review When I open my queue Then each shows the event name, date and time, every confirmed venue with its capacity, layout and known restrictions, expected attendance, accessibility requirements, equipment and its placement, and the time it entered Safety Review, oldest first
@@ -3254,41 +3309,41 @@
 - Confirm every decision is in the activity log</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-70, T-71, T-72, T-73, T-74, O-39, O-40, O-41, O-42, O-43</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register once for a confirmed Event and select the Sessions I will attend so that my place is reserved across the Event I chose.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open Event
 Given an Event is Confirmed, registration is open, and selected Sessions have capacity When I submit the required registration information and select one or more Sessions Then one active Event-level registration records those Sessions and I receive a confirmation with the Event and selected Session details
@@ -3309,43 +3364,43 @@
 - See the primary Event venue and the venue for each selected Session</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-35, C-67, C-97, C-107, T-68, T-78, T-79, T-85</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want the system to enforce each selected Session's approved layout capacity and the combined Event capacity so that registrations do not exceed either limit.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Both capacity limits enforced
 Given a registration selects one or more Sessions When the request is within each selected Session's approved layout capacity and within the combined Event capacity Then it may be confirmed; if either limit would be exceeded it is not confirmed as an approved seat (C-78, T-85)
@@ -3371,43 +3426,43 @@
 - Allow manual VIP additions only within both limits and block them at either limit</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, C-78, C-98, T-30, T-31, T-50, T-85, B-11, O-50</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set one registration and withdrawal window for the Event so that attendees can select Sessions within a consistent Event-level period.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the Event-level registration opening date has not been reached When an Attendee views the Event Then registration is shown as not yet open and the opening date is stated
@@ -3426,43 +3481,43 @@
 - Warn when the closing date is after the Event has started</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42, T-79, T-85</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given the combined Event capacity is full and its Event-level waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released (Session-specific waiting-list behavior remains open under O-50)
@@ -3481,43 +3536,43 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10, O-50</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my Event registration so that my Event place and places in all selected Sessions are released together.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn from Event and Sessions
 Given I have an active Event registration selecting one or more Sessions and the withdrawal deadline has not passed When I withdraw Then the Event registration is cancelled and its approved places are released from every selected Session and from the combined Event capacity
@@ -3529,43 +3584,43 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10, T-79, T-85</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -3581,43 +3636,43 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -3635,43 +3690,43 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my Event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the Event
@@ -3693,43 +3748,43 @@
 - Confirm Pending requests become Obsolete with history when the Event becomes Completed or Cancelled</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, C-77, T-16, T-88</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to identify which Session arrangements a change affects so that I re-check the right bookings and reservations.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Session attendance beyond capacity flagged
 Given a Session has a confirmed venue booking When its expected attendance changes Then each booking whose own headcount is set uses that headcount, otherwise it uses the Session attendance; only a booking whose governing headcount exceeds capacity is flagged and Venue Staff are notified
@@ -3752,43 +3807,43 @@
 - Notify staff responsible for the affected arrangements</t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27, C-107, T-79</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an Event and release its Session arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled and Session arrangements released
 Given an Event Organiser requests cancellation When I cancel the Event and record a reason Then its status becomes Cancelled, all Session venue bookings and equipment reservations are released, calendars/availability are updated, and affected staff are notified
@@ -3809,44 +3864,44 @@
 - Close Pending change requests as Obsolete with history</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, C-77, T-07, T-48, T-79, T-88</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>E10-S05</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Handle a venue lost from a confirmed event</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
 Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Lost venue flags the event
 Given my event has a Pending or Confirmed venue booking When Venue Staff mark that venue unavailable over the booking's period (E05-S06) Then I am notified, the booking shows as Conflicting on the event, and the event is flagged as needing alternative arrangements while its status and every other arrangement stay as they were (assumes O-24)
@@ -3864,43 +3919,43 @@
 - Confirm the Organiser and registered Attendees are told of the venue change only when it actually happens</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>C-66, C-61, T-28, T-67, T-73, T-74, O-24, O-25</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -3928,43 +3983,43 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70, C-70, T-71</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log; access-denial entries are not shown in that log
@@ -3986,15 +4041,73 @@
 - Verify denial and deactivation entries in a controlled test database; no Administrator sign-in is required</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>T-04, T-75, T-76</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Le Xin</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>E14 Audit &amp; History</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>E14-S03</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Read edited Activity log dates and times in Singapore time</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser or the assigned Event Coordinator, I want edited date/time values in my existing event Activity log to be readable in Singapore time so that I can understand the recorded edit without interpreting raw UTC strings.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Both existing readers see Singapore time
+Given an authorised Organiser or assigned Coordinator opens the existing event Activity log When an entry displays an edited date/time field value Then each date/time value already displayed by that view uses the existing shared Singapore formatter, including both old and new values where already shown, independently of the browser timezone; 2026-10-15T09:30:00Z represents 15 October 2026 at 17:30 Singapore time, not 16 October. Existing field keys are startAt, endAt and registrationDates; registrationDates stores "opensAt to closesAt", so both endpoints are formatted for display without changing that stored string.
+Scenario 2 - Singapore calendar rollover
+Given an edited date/time value is 2026-10-15T18:30:00Z When either view displays it Then it represents 16 October 2026 at 02:30 Singapore time; the calendar date as well as the hour is converted correctly.
+Scenario 3 - Missing and invalid values keep the existing contract
+Given a date/time value is missing or invalid When formatting is needed Then formatDate retains its existing "Not recorded" result; each view retains its existing omission/label-only behavior for absent change values, without throwing, inventing a date or introducing a new fallback.
+Scenario 4 - Other values and existing display paths unchanged
+Given an entry contains ordinary text, a status change or a venue hold expiry When either view renders it Then ordinary text remains text, existing status labels/badges remain unchanged, and existing hold-expiry formatting and behavior are preserved; the correction is field-aware, not conversion of every date-looking string.
+Scenario 5 - Audit evidence and access unchanged
+Given the existing event access rules apply When either permitted reader views or reloads the formatted log Then stored UTC old_value/new_value and occurred_at, actor and action remain unchanged and immutable; unauthorised readers remain refused and access-denial entries remain hidden from event logs, with no new audit viewer or permissions.
+Checklist
+- Scope implementation to the edited date/time value rendering in frontend/src/features/organiser/ClientEvents.tsx and frontend/src/features/events/ActivityLog.tsx using shared formatDate
+- Cover both views, same-day and rollover boundaries, missing/invalid inputs, other values and immutable/access-preserving reads with TC_E14S03_01 to _06
+- Do not add before/after history to a view that does not already show it; wider E14-S01 history remains separate
+- Exclude notification "Changed at ...Z" text, unrelated action/field labels, global viewers, new notifications and changes to stored audit data or hold-expiry behavior
+- Obtain human code/test review and future T-65/T-93 manual evidence; these planned cases are not execution evidence</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>T-93</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>Le Xin</t>
         </is>
@@ -4011,7 +4124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5484,25 +5597,72 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
+          <t>E03 Review, Coordination &amp; Status</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>E03-S12</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Show consistent Organiser save success status</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser, I want confirmation of a saved event edit to use the shared success Alert so that I can recognise the same clear save outcome used on the Coordinator's event page.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Shared success Alert after a saved edit
+Given I may edit an event When a changed field saves successfully Then the event detail shows the existing field-specific saved message through the shared Alert with tone="success", retaining role="status" rather than replacing it with an urgent alert or plain paragraph.
+Scenario 2 - Saved data and audit survive reload
+Given an allowed event edit succeeds When the record reloads and I reopen it Then the changed value is retained and its existing activity-log entry remains available, with no extra save or audit write caused by rendering the confirmation.
+Scenario 3 - Failure cannot report success
+Given a new edit is invalid or its save request fails When I attempt to save Then the existing validation or error feedback remains and no success Alert claims that attempt was saved; starting a new edit clears the previous save confirmation.
+Scenario 4 - Cancellation and permissions unchanged
+Given I cancel an edit or attempt a field I cannot edit under the current event status and access rules When the attempt ends Then cancellation produces no save confirmation or mutation, and existing restrictions and change-request routing remain in force.
+Checklist
+- Reuse frontend/src/shared/feedback.tsx Alert in frontend/src/features/organiser/ClientEvents.tsx; preserve field-specific text and polite status semantics
+- Cover successful save/reload/audit, invalid input, failed request after a prior success, cancellation and restricted fields with TC_E03S12_01 to _05
+- Leave the Coordinator save flow, all other Organiser workflows, permissions and notifications unchanged; no redesign or new notification
+- Obtain human review of code and test cases and future manual evidence before claiming delivery; this definition does not execute those cases</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>T-93</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>E04-S01</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Record the event programme</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to record the programme for my event, including sessions and breaks, so that ConnectSphere can plan the venue and support around it.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Programme item added
 Given I am editing my event When I add a programme item with a title, start time and end time Then it appears in the event in chronological order
@@ -5512,39 +5672,39 @@
 Given two programme items overlap When I save them Then I am warned of the overlap</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>T-19</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>E04 Programme &amp; Sessions</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>E04-S02</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Create a multi-session event</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to define an event made up of one or more Sessions so that each Session's requirements can be planned separately.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Sessions hold their own requirements
 Given I am creating an event When I add one or more Sessions Then each Session stores its date, time, expected attendance, venue requirements, and equipment requirements beneath the Event
@@ -5564,39 +5724,39 @@
 - Delete a Session and release its confirmed booking with notification and history</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>C-19, C-62, C-107, T-48, T-79, T-85</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>E05-S01</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Maintain the venue catalogue</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to add and update venue records so that Event Coordinators search against accurate information.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Venue added and searchable
 Given I am adding a venue When I save it with location, capacity, facilities, accessibility features, supported layouts and operating hours Then it becomes searchable by Event Coordinators
@@ -5615,39 +5775,39 @@
 - Be blocked from retiring a venue with future bookings, with those bookings identified</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>T-13, T-18, B-05</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>E05-S02</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Match layout requirements to venue capacity</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the room layouts supported by a venue and the maximum capacity for each layout, so that Event Coordinators only consider arrangements the venue can accommodate.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Layout and capacity stored
 Given I am editing a venue When I add a supported layout with its maximum capacity Then it is stored against that venue
@@ -5663,39 +5823,39 @@
 - Be warned when adding a layout that already exists</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>T-45, B-07</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>E05-S03</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>View the venue availability calendar</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to view a venue's calendar so that I can see when the venue is free, pending, confirmed or blocked.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Four states distinguishable
 Given a venue has bookings and blocks in a period When I open its calendar for that period Then each entry is shown as Free, Tentative, Confirmed or Blocked, and the states are visually distinguishable
@@ -5712,39 +5872,39 @@
 - See periods I cannot view marked unavailable without any event detail</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>C-40, C-60, T-17, T-49</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>E05-S04</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Block a venue for maintenance</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to block a venue for maintenance, renovation or safety reasons so that it is not offered for events during that period.</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Free period blocked
 Given a venue has no bookings in a period When I block that period and record a reason Then the venue no longer appears as available for those dates
@@ -5760,40 +5920,40 @@
 - Confirm affected Event Coordinators are notified when a block affects an upcoming event</t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>E05-S05</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Apply setup and turnaround time</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to record the setup and turnaround time each venue requires so that every availability and conflict check accounts for the time needed to prepare the room before an event and reset it afterwards.
 Returned to Release 1 by the Week 7 Customer Changes (C-65). The five-point estimate is the one carried from the original backlog and is re-estimated at Sprint 3 planning (T-73). Scenario 3 lives here rather than in E05-S03, and Scenario 7 here rather than in E06-S01, because both of those stories are Done (T-74). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md` and are amended if the customer answers differently.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Buffers recorded on the venue
 Given I am creating or editing a venue When I enter a setup time and a turnaround time in whole minutes, either of which may be 0, and save Then both values are stored against the venue and shown on its detail, and every venue that existed before this story has both values at 0
@@ -5817,40 +5977,40 @@
 - Never have a booking released automatically because a buffer changed</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>C-65, T-66, T-73, T-74, O-20, O-21, O-22 (supersedes C-18, C-38)</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>E05 Venue Catalogue &amp; Availability</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>E05-S06</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mark a venue temporarily unavailable over existing bookings</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to mark a venue temporarily unavailable for maintenance, equipment failure, renovation, a safety concern or another operational reason, even when events are already booked in it, so that affected bookings are identified and their Coordinators can arrange an alternative without the events themselves being cancelled.
 New story from the Week 7 Customer Changes (C-66). It supersedes E05-S04 Scenario 2, which refused a block over a confirmed booking; E05-S04 is in the Sprint 2 sprint backlog and is not edited (T-67, T-74). Estimate to be set by planning poker at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Unavailability recorded with a reason
 Given I am viewing a venue When I mark it unavailable for a period and choose a reason category from maintenance, equipment failure, renovation, safety concern or other, with a free-text note Then the unavailability is saved with the period, the category, the note and my identity, and the calendar shows the period as Blocked
@@ -5874,37 +6034,37 @@
 - Confirm E05-S04's existing block, shorten and remove behaviour still works for periods with no bookings</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>C-66, C-48, C-61, T-28, T-67, T-74, O-23, O-24, O-25, O-26</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr"/>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>E06-S01</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Search for suitable venues</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search venues by date, time, attendance, capacity, layout, accessibility and facilities so that I can shortlist options for an event quickly.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Matching venues listed
 Given venues exist that match all my criteria and are available When I run the search Then those venues are listed with their capacity, layouts and facilities
@@ -5923,39 +6083,39 @@
 - Apply several filters together in one search</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>B-08</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>E06-S02</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Check venue suitability against event requirements</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to compare a venue against the event's recorded requirements so that I do not request a venue that cannot meet them.</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Suitability shown for the event
 Given an event has recorded requirements When I view a venue in the context of the event Then a suitability status is shown for the event
@@ -5984,39 +6144,39 @@
 - Identify outside operating hours as an advisory failure in E06-S02, without adding that rule to E06-S01</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C-06, T-13, T-48 (supersedes T-21), T-77, B-08</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr"/>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>E06-S03</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Request a venue booking</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to submit a venue booking request for an event so that Venue Staff can review it and decide whether the venue can be provided.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request created as Pending
 Given an event has recorded requirements and no pending request When I submit a booking request for a venue Then the request is created with status Pending, the venue calendar shows the period as Tentative, and the Venue Staff are notified
@@ -6077,39 +6237,39 @@
 - Complete TC_E06S03_09 to _13 under the current Sprint 3 plan; record anything unfinished honestly at sprint close (PO confirmation, 16 October; T-94)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-17, C-37, C-46, C-60, T-20, T-49, C-65, T-66, C-67, T-68, T-78, O-27, O-29, O-30, T-94, T-95, T-96</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr"/>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>E06-S04</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Decide on a venue booking request</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to approve or reject booking requests and record my reasoning so that Coordinators receive a clear, traceable decision.</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request approved and confirmed
 Given a booking request is pending and the venue is free for the period When I approve it Then the booking becomes Confirmed, the venue calendar is updated and the Coordinator is notified
@@ -6133,40 +6293,40 @@
 - Verify all three booking-log outcomes under TC_E06S04_05, TC_E06S04_06 and TC_E06S04_07</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>C-08, T-39, C-65, T-66, T-75, T-76</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr"/>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>E06-S05</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Hold a venue tentatively</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to place a tentative hold on a venue so that it is not taken by another event while the arrangements are still being finalised, and I want the hold to expire at a known time so that venues are not reserved indefinitely.
 The expiry scenarios come from the Week 7 Customer Changes (C-68, T-69) and reverse the earlier position that no expiry was required (C-01, C-16, C-60, T-49). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Tentative hold placed
 Given a venue is free for the period When I place a tentative hold Then the calendar shows the period as Tentative, the hold is recorded against my event, and the hold carries an expiry date and time set to 48 hours from creation by default, which Venue Staff may change on the hold (assumes O-31)
@@ -6199,39 +6359,39 @@
 - Confirm Venue Staff can extend an unexpired hold and the extension is logged (assumes O-34)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>C-01, C-16, C-37, C-60, T-49, C-65, T-66, C-68, T-69, T-78, T-92, O-31, O-32, O-33, O-34</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>E06 Venue Search &amp; Booking</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>E06-S06</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Prevent double-booking of a venue</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to be blocked from approving a booking that overlaps an existing confirmed booking for the same venue so that a venue is never committed to two events at once.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Overlapping approval blocked
 Given a venue has a confirmed booking When I attempt to approve another request overlapping that period Then approval is blocked and the conflicting booking is identified
@@ -6252,39 +6412,39 @@
 - Confirm no venue ever holds two confirmed bookings over the same period</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>C-46, T-22, C-65, T-66, C-67, T-68</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr"/>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>E07-S01</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Maintain the equipment catalogue</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to maintain equipment records including type, quantity, location and operational status so that availability checks are based on accurate data.</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item added and reservable
 Given I am adding an equipment item When I save its type, description, quantity, location and operational status Then it becomes available for reservation
@@ -6301,39 +6461,39 @@
 - Confirm retired items no longer appear in availability checks</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>E07-S02</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Request equipment for an event</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record the equipment an event needs, with quantities, so that Technical Support Staff can check whether it can be provided.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Equipment recorded against an event
 Given I am planning an approved event When I add equipment items with quantities to an event Then the request is saved against the event and the Technical Support Staff are notified
@@ -6349,39 +6509,39 @@
 - Amend or remove an equipment request before it is reserved</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>T-25</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr"/>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>E07-S03</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Check equipment availability</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to see how much of an item is free for a given date and time so that I can decide whether a request can be met.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reserved and faulty stock excluded
 Given some items are reserved for other events in the period When I check availability Then the free quantity excludes those reservations and any items marked damaged or under maintenance
@@ -6397,39 +6557,39 @@
 - Confirm the same item can serve two events at non-overlapping times</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>E07-S04</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Reserve equipment for an event</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to reserve equipment for an event so that limited equipment is not committed to two events at the same time.</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Full reservation recorded
 Given sufficient equipment is free for the period When I reserve the requested quantity Then the reservation is recorded against the event and the Event Coordinator is notified
@@ -6448,39 +6608,39 @@
 - Receive confirmation showing the event, date, time, item and quantity</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>C-21, T-24, B-09</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr"/>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>E07-S05</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Mark equipment as unavailable</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to mark equipment as damaged or under maintenance so that it is not treated as available for events.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Item marked unavailable
 Given an item has no reservations in the period When I mark it unavailable with a reason and a period Then it is excluded from availability checks for that period
@@ -6493,39 +6653,39 @@
 - Return an item to service, restoring it to availability checks</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>B-04</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr"/>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>E07-S06</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Request technical support for an event</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to request on-site technical support for an event and describe what is needed so that suitable staff can be allocated.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Support request recorded
 Given an event requires technical support When I submit a request describing the support and the times it is needed Then the Technical Support Staff are notified and the request is recorded against the event
@@ -6541,39 +6701,39 @@
 - Mark an event as requiring no technical support</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>C-22, T-23</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr"/>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>E07-S07</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Assign and manage technical staff for an event</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want to assign and manage available colleagues to support an event so that the right people are on site at the right time.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Available colleague assigned
 Given an event has an open technical support request and a colleague is available for its times When I assign them Then they are notified and the assignment appears on their schedule
@@ -6592,39 +6752,39 @@
 - Confirm the staff member is notified when assigned or removed</t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>C-39</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr"/>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>E07-S08</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Link equipment requests and reservations to Sessions</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want equipment requests and reservations to identify the Session they support so that availability and fulfilment use the correct Session period.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Request linked to its Session
 Given an Event has multiple Sessions When an Event Coordinator records equipment needed for one Session Then the request is linked to that Session and remains part of the Event
@@ -6641,37 +6801,37 @@
 - Keep technical-support staff assignment event-level</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>C-107, T-74, T-79</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr"/>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>E07 Equipment &amp; Technical Support</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>E07-S09</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Preserve reservation warnings when stock reductions overlap withdrawals</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want catalogue stock reductions to account for dated equipment withdrawals so that reservations which no longer fit are flagged and their Coordinators are notified.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reduced usable stock flags reservations
 Given an item has total stock 10, four units withdrawn and five units reserved for the same future period When I reduce total stock to 8 Then the save succeeds, the reservation remains reserved but is marked for review, and its assigned active Coordinator receives one notification and an outbox record
@@ -6687,37 +6847,37 @@
 - Roll back stock, flags and notification/outbox writes together on failure</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>C-07, C-20</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>E08-S01</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>View readiness of an event</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see whether venue, equipment and technical support are ready so that I know what still needs my attention.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Arrangement states shown
 Given an event is in planning When I open its readiness view Then each arrangement is shown as complete, in progress or not started
@@ -6725,39 +6885,39 @@
 Given an arrangement is not started When I view it Then the responsible role and the action required are shown</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>E08-S02</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Track outstanding actions across events</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a list of upcoming events with incomplete arrangements so that nothing is overlooked before an event takes place.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete events listed by date
 Given I have upcoming events with incomplete arrangements When I open my outstanding actions list Then those events are listed with the specific incomplete items, ordered by event date
@@ -6765,40 +6925,40 @@
 Given an event is close to its date and arrangements are still incomplete When I view the list Then that event is highlighted as urgent</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>C-28</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr"/>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>E08-S03</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Confirm an event</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to confirm an event once the event's arrangements are complete so that the Event Organiser and Attendees can rely on the details.
 Amended in place for the Week 7 Customer Changes (C-70, T-71; this story is To Do, T-74). Completing the arrangements no longer sets Confirmed directly: it lets the Coordinator submit the event for its Operational Safety Check, which moves it to the new Safety Review status, and the Safety Officer's approval (E08-S06) is what sets Confirmed. The readiness checks below are unchanged in substance; what they now gate is the submission. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - All arrangements complete, event submitted for safety review
 Given every venue booking on the event is Confirmed or has been withdrawn, at least one is Confirmed, its full requested equipment is reserved and any requested technical support is assigned When I submit the event for its Operational Safety Check Then the status becomes Safety Review, the Safety Officer is notified, the Organiser is told the event is awaiting its safety check, and the event becomes Confirmed only when the Safety Officer approves it (E08-S06) (C-67, T-68, C-70, T-71; assumes O-28, O-39, O-40)
@@ -6824,39 +6984,39 @@
 - Confirm the Event Organiser is notified with the full confirmed details</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>C-13, C-39, C-59, C-63, T-02, T-24, T-27, C-67, T-68, O-28, C-70, T-71, T-74, O-39, O-40</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>E08-S04</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Revert a confirmed event to planning</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want a confirmed event to return to Planning when an arrangement requires it so that the system reflects the event's readiness and starts safety review at the right time.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Manual reversion records a reason
 Given an event is Confirmed When I deliberately revert it to Planning and record a reason Then the status becomes Planning and the Event Organiser is notified with the reason
@@ -6877,39 +7037,39 @@
 - Retain earlier safety decisions in history without reusing them</t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>C-48, T-03, T-28, C-70, T-71, C-120, T-81, C-132, T-82</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr"/>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>E08-S05</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Complete an event</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want an event to become Completed once it has taken place so that attendance can be recorded and the event closed.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Auto-completed after the end time
 Given an event is Confirmed and its end time has passed When the system next evaluates it Then the status becomes Completed
@@ -6927,40 +7087,40 @@
 - Confirm the transition is recorded in the activity log</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>T-03, T-26, T-48</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr"/>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>E08 Readiness &amp; Confirmation</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>E08-S06</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Conduct the Operational Safety Check as the Safety Officer</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>As a Safety Officer, I want to review the operational safety of each event whose venue and technical arrangements are confirmed, and approve it, reject its safety arrangement or request changes, so that no event proceeds to preparation until it is safe to run.
 New story from the Week 7 Customer Changes (C-70) and the seventh role (T-72). The Safety Review status it works on sits between Planning and Confirmed as an interim placement (T-71); O-39 asks the customer to confirm. The customer guarantees a response, so there is no timeout path. Estimate at Sprint 3 planning (T-73). Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events awaiting review listed with what the check needs
 Given events are in Safety Review When I open my queue Then each shows the event name, date and time, every confirmed venue with its capacity, layout and known restrictions, expected attendance, accessibility requirements, equipment and its placement, and the time it entered Safety Review, oldest first
@@ -6993,37 +7153,37 @@
 - Confirm every decision is in the activity log</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>C-70, T-71, T-72, T-73, T-74, O-39, O-40, O-41, O-42, O-43</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr"/>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>E09-S01</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Register for an event</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to register once for a confirmed Event and select the Sessions I will attend so that my place is reserved across the Event I chose.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Place reserved in an open Event
 Given an Event is Confirmed, registration is open, and selected Sessions have capacity When I submit the required registration information and select one or more Sessions Then one active Event-level registration records those Sessions and I receive a confirmation with the Event and selected Session details
@@ -7044,39 +7204,39 @@
 - See the primary Event venue and the venue for each selected Session</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>C-35, C-67, C-97, C-107, T-68, T-78, T-79, T-85</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>E09-S02</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Enforce registration capacity</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want the system to enforce each selected Session's approved layout capacity and the combined Event capacity so that registrations do not exceed either limit.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Both capacity limits enforced
 Given a registration selects one or more Sessions When the request is within each selected Session's approved layout capacity and within the combined Event capacity Then it may be confirmed; if either limit would be exceeded it is not confirmed as an approved seat (C-78, T-85)
@@ -7102,39 +7262,39 @@
 - Allow manual VIP additions only within both limits and block them at either limit</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>C-05, C-58, C-78, C-98, T-30, T-31, T-50, T-85, B-11, O-50</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr"/>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>E09-S03</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Control the registration period</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to set one registration and withdrawal window for the Event so that attendees can select Sessions within a consistent Event-level period.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before registration opens
 Given the Event-level registration opening date has not been reached When an Attendee views the Event Then registration is shown as not yet open and the opening date is stated
@@ -7153,39 +7313,39 @@
 - Warn when the closing date is after the Event has started</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>C-24, C-44, T-42, T-79, T-85</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr"/>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>E09-S04</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Join the waiting list</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to join the waiting list when an event is full so that I can still attend if a place is released.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Joined a full event's list
 Given the combined Event capacity is full and its Event-level waiting list is enabled When I join the waiting list Then I am added and told I will be notified when a place is released (Session-specific waiting-list behavior remains open under O-50)
@@ -7204,39 +7364,39 @@
 - Confirm no waiting list is offered when the Organiser has disabled it</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>C-23, T-33, T-46, B-10, O-50</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr"/>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>E09-S05</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Withdraw my registration</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>As an Attendee, I want to withdraw my Event registration so that my Event place and places in all selected Sessions are released together.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registration withdrawn from Event and Sessions
 Given I have an active Event registration selecting one or more Sessions and the withdrawal deadline has not passed When I withdraw Then the Event registration is cancelled and its approved places are released from every selected Session and from the combined Event capacity
@@ -7248,39 +7408,39 @@
 - Be refused after the withdrawal deadline, with a contact provided</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>C-24, T-48, B-10, T-79, T-85</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>E09-S06</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Record attendance</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to record which registered Attendees actually attended the event so that registration and attendance can be distinguished.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Attendance marked after completion
 Given an event has status Completed When I mark an Attendee as attended for an event Then their record shows attended and the registration figure is unchanged
@@ -7296,39 +7456,39 @@
 - View registration and attendance counts side by side for the event</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>C-45</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr"/>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>E09 Attendee Registration</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>E09-S07</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>View registrations for my event</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to view the list of Attendees registered for my event so that I can plan for the numbers attending the event.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Registrations grouped by event
 Given Attendees have registered for my event When I open its registration list Then I see each Attendee's name, email address and contact number
@@ -7346,39 +7506,39 @@
 - Be refused access to registration lists for events I do not manage</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="G67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32, O-05</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr"/>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>E10-S01</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Request a change after submission</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to request a change to my event after it has been submitted or confirmed so that the arrangements reflect what I now need.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Change request recorded
 Given my Event has been approved or confirmed When I submit a change request describing what should change Then the assigned Coordinator is notified and the request is recorded against the Event
@@ -7400,39 +7560,39 @@
 - Confirm Pending requests become Obsolete with history when the Event becomes Completed or Cancelled</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="G68" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>C-14, C-52, C-54, C-77, T-16, T-88</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>E10-S02</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Distinguish minor edits from arrangement-affecting changes</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want the system to identify which Session arrangements a change affects so that I re-check the right bookings and reservations.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Session attendance beyond capacity flagged
 Given a Session has a confirmed venue booking When its expected attendance changes Then each booking whose own headcount is set uses that headcount, otherwise it uses the Session attendance; only a booking whose governing headcount exceeds capacity is flagged and Venue Staff are notified
@@ -7455,39 +7615,39 @@
 - Notify staff responsible for the affected arrangements</t>
         </is>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>C-05, T-16, B-05, B-11, C-67, T-68, O-27, C-107, T-79</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr"/>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>E10-S03</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Reschedule an event</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to reschedule an Event while identifying the Session arrangements that must be reconfirmed so that it can still take place when the original dates no longer work.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Session date change flags its arrangements
 Given an Event has confirmed Session venue bookings or equipment reservations When I change one Session's date or time Then only that Session's existing arrangements are flagged for reconfirmation and are not moved silently
@@ -7504,39 +7664,39 @@
 - Close Pending change requests as Obsolete when the Event becomes Completed or Cancelled</t>
         </is>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="G70" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>C-25, O-18, C-77, C-107, T-79, T-88</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr"/>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>E10-S04</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Cancel an event</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to cancel an Event and release its Session arrangements so that venues and equipment do not stay committed to something that will not happen.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Event cancelled and Session arrangements released
 Given an Event Organiser requests cancellation When I cancel the Event and record a reason Then its status becomes Cancelled, all Session venue bookings and equipment reservations are released, calendars/availability are updated, and affected staff are notified
@@ -7557,40 +7717,40 @@
 - Close Pending change requests as Obsolete with history</t>
         </is>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="G71" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>C-14, C-54, C-77, T-07, T-48, T-79, T-88</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr"/>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>E10 Changes, Rescheduling &amp; Cancellation</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>E10-S05</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Handle a venue lost from a confirmed event</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when a venue becomes unavailable for one of my events and to find and request a replacement from the event itself, so that I can arrange an alternative before Attendees are affected while the original event information is preserved.
 Returned to Release 1 by the Week 7 Customer Changes (C-66, T-67). The three-point estimate is carried from the original backlog and re-estimated at Sprint 3 planning (T-73). The alert itself is raised by E05-S06; this story is what the Coordinator does with it. Scenarios tagged "(assumes O-xx)" are written to the default recorded in `docs/bdr/C-open-questions.md`.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Lost venue flags the event
 Given my event has a Pending or Confirmed venue booking When Venue Staff mark that venue unavailable over the booking's period (E05-S06) Then I am notified, the booking shows as Conflicting on the event, and the event is flagged as needing alternative arrangements while its status and every other arrangement stay as they were (assumes O-24)
@@ -7608,39 +7768,39 @@
 - Confirm the Organiser and registered Attendees are told of the venue change only when it actually happens</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>C-66, C-61, T-28, T-67, T-73, T-74, O-24, O-25</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr"/>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>E11-S01</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Notify users about events they are involved in</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>As a user involved in an event, I want to be notified when its status or arrangements change so that I do not have to keep checking the system and nobody continues working from outdated information.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change notified
 Given I am a recipient under the approved routing matrix When an event status changes or a booking decision is made Then I receive a notification stating what changed, when, and which event it concerns, unless I performed the action myself
@@ -7668,39 +7828,39 @@
 - Mark a notification as read</t>
         </is>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>C-04, C-29, C-53, T-35, T-36, T-44, T-48, T-64, C-68, T-69, O-33, C-69, T-70, C-70, T-71</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr"/>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>E11-S03</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Receive reminders about upcoming commitments</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>As a Technical Support Staff member, I want reminders about upcoming events I am supporting so that equipment and support are prepared in time.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Reminder lists requirements
 Given I am assigned to an upcoming event When the reminder point before it is reached Then I receive a reminder listing the equipment and support required
@@ -7708,39 +7868,39 @@
 Given an event is cancelled before its reminder is due When the reminder point is reached Then no reminder is sent</t>
         </is>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="G74" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>C-28, O-11</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr"/>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>E11 Notifications &amp; Reminders</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>E11-S04</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Alert on incomplete arrangements</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to be alerted when an upcoming event still has incomplete arrangements so that I can act while there is still time.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Incomplete items named
 Given an upcoming event has an incomplete essential arrangement When the alert point before it is reached Then I receive an alert naming the incomplete items
@@ -7748,39 +7908,39 @@
 Given all arrangements are completed before the alert point When the alert point is reached Then no alert is sent</t>
         </is>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="G75" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr"/>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>E12-S01</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>View my events in a calendar</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see my events in a calendar so that I can plan my workload across the coming weeks.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Events shown on their dates
 Given I have events spread across several weeks When I open the calendar Then my events appear on their dates with their status indicated
@@ -7788,39 +7948,39 @@
 Given an event spans several days When I view the calendar Then it is shown across all its days rather than only the first</t>
         </is>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="G76" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr"/>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>E12-S02</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Search and filter events</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to search events by name, client, date, venue, status, category or assigned Coordinator so that I can find a specific event quickly.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Permitted matches returned
 Given events match my criteria When I search Then only matching events that I am permitted to see are returned
@@ -7830,39 +7990,39 @@
 Given I apply several filters at once When I search Then all the filters are applied together</t>
         </is>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="G77" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr"/>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>E12-S03</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>See my work on a role-based dashboard</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want a dashboard showing booking requests awaiting my decision and upcoming venue preparations so that I can see my outstanding work in one place.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Pending decisions listed
 Given booking requests are pending my decision When I open my dashboard Then they are listed with event name, venue, dates and how long each has been waiting
@@ -7870,39 +8030,39 @@
 Given I have no outstanding items When I open my dashboard Then an empty state is shown rather than an error</t>
         </is>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="G78" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr"/>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>E12 Calendar, Search &amp; Dashboards</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>E12-S04</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Use the system on a mobile device</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to use the system on my phone while preparing a venue so that I can check and update arrangements without returning to a desk.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Readable without horizontal scrolling
 Given I open the system on a mobile device When I view my dashboard, an event or a venue calendar Then the content is readable and usable without horizontal scrolling
@@ -7910,39 +8070,39 @@
 Given I am working on a mobile device When I update a preparation status Then the update is saved exactly as it would be on a desktop</t>
         </is>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="G79" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr"/>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>E13-S01</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Generate an event report</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to generate a summary report for an event so that I can share the arrangements at operational meetings.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Generate a downloadable report containing event name, date and time, venue, equipment list, assigned technical support and total registered Attendees
@@ -7951,39 +8111,39 @@
 - Show a clear error with a retry option if generation fails</t>
         </is>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="G80" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr"/>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>E13-S02</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Review venue usage over a period</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>As a Venue Staff member, I want to review venue bookings and usage over a chosen period so that I can plan maintenance and identify under-used spaces.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Select a custom date range with start and end dates
@@ -7993,39 +8153,39 @@
 - See an informative empty state when no records match</t>
         </is>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="G81" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>C-27, O-01</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr"/>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>E13 Reporting &amp; Export</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>E13-S03</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Export attendee registration information</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>As an Event Organiser, I want to export the registration list for my event so that I can prepare badges and catering numbers.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Checklist
 - Export registrations only for events the Organiser manages
@@ -8033,39 +8193,39 @@
 - Exclude sensitive personal data from the generated file</t>
         </is>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="G82" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>C-26, T-32</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr"/>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>E14-S01</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>View an event's change history</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>As an Event Coordinator, I want to see how an event's important information has changed over time so that I can explain how the current arrangements were reached.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Before and after values listed
 Given an event's date, venue, attendance or status has changed When I open its change history Then each change is listed with the previous value, the new value, who made it and when
@@ -8073,39 +8233,39 @@
 Given I am not permitted to view a particular change When I open the history Then that entry is not shown to me</t>
         </is>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="G83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr"/>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>E14 Audit &amp; History</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>E14-S02</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Record significant actions in an activity log</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>As a ConnectSphere staff member, I want significant actions to be recorded so that we can determine who did what and when.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Scenario 1 - Status change recorded
 Given an event status changes When the change completes Then an entry is recorded with the actor, the action, the affected event and the time, and an Event Coordinator permitted to view the event can read it in the event Activity log; access-denial entries are not shown in that log
@@ -8127,15 +8287,65 @@
 - Verify denial and deactivation entries in a controlled test database; no Administrator sign-in is required</t>
         </is>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="G84" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>T-04, T-75, T-76</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>E14 Audit &amp; History</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>E14-S03</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Read edited Activity log dates and times in Singapore time</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>As an Event Organiser or the assigned Event Coordinator, I want edited date/time values in my existing event Activity log to be readable in Singapore time so that I can understand the recorded edit without interpreting raw UTC strings.</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Scenario 1 - Both existing readers see Singapore time
+Given an authorised Organiser or assigned Coordinator opens the existing event Activity log When an entry displays an edited date/time field value Then each date/time value already displayed by that view uses the existing shared Singapore formatter, including both old and new values where already shown, independently of the browser timezone; 2026-10-15T09:30:00Z represents 15 October 2026 at 17:30 Singapore time, not 16 October. Existing field keys are startAt, endAt and registrationDates; registrationDates stores "opensAt to closesAt", so both endpoints are formatted for display without changing that stored string.
+Scenario 2 - Singapore calendar rollover
+Given an edited date/time value is 2026-10-15T18:30:00Z When either view displays it Then it represents 16 October 2026 at 02:30 Singapore time; the calendar date as well as the hour is converted correctly.
+Scenario 3 - Missing and invalid values keep the existing contract
+Given a date/time value is missing or invalid When formatting is needed Then formatDate retains its existing "Not recorded" result; each view retains its existing omission/label-only behavior for absent change values, without throwing, inventing a date or introducing a new fallback.
+Scenario 4 - Other values and existing display paths unchanged
+Given an entry contains ordinary text, a status change or a venue hold expiry When either view renders it Then ordinary text remains text, existing status labels/badges remain unchanged, and existing hold-expiry formatting and behavior are preserved; the correction is field-aware, not conversion of every date-looking string.
+Scenario 5 - Audit evidence and access unchanged
+Given the existing event access rules apply When either permitted reader views or reloads the formatted log Then stored UTC old_value/new_value and occurred_at, actor and action remain unchanged and immutable; unauthorised readers remain refused and access-denial entries remain hidden from event logs, with no new audit viewer or permissions.
+Checklist
+- Scope implementation to the edited date/time value rendering in frontend/src/features/organiser/ClientEvents.tsx and frontend/src/features/events/ActivityLog.tsx using shared formatDate
+- Cover both views, same-day and rollover boundaries, missing/invalid inputs, other values and immutable/access-preserving reads with TC_E14S03_01 to _06
+- Do not add before/after history to a view that does not already show it; wider E14-S01 history remains separate
+- Exclude notification "Changed at ...Z" text, unrelated action/field labels, global viewers, new notifications and changes to stored audit data or hold-expiry behavior
+- Obtain human code/test review and future T-65/T-93 manual evidence; these planned cases are not execution evidence</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>T-93</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
